--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1496.72</v>
+        <v>1694.28</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1496.72</v>
+        <v>1694.28</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>57170.26</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>11393.66</v>
+        <v>11591.22</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>47000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>4 de 58</t>
+          <t>5 de 58</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4417,7 +4417,7 @@
         <v>6961.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>10000</v>
@@ -5757,7 +5757,7 @@
         <v>57170.26</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>11591.22</v>
+        <v>26277.17</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>47000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RUALES SARAGURO JIMMY JAVIER</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3360,13 +3360,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>50.24</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>3704.28</v>
+        <v>0</v>
       </c>
       <c r="P48" s="2" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
+          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
+          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
+          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>SOPLIN MENDOZA TABITA</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SOPLIN MENDOZA TABITA</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
+          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="P57" s="2" t="n">
         <v>0</v>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
+          <t>VIVANCO MALDONADO SILVANA MARILY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>24.88</v>
+        <v>0</v>
       </c>
       <c r="P58" s="2" t="n">
         <v>0</v>
@@ -3979,144 +3979,84 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>VIVANCO MALDONADO SILVANA MARILY</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>1 de 58</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>1 de 58</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>1 de 58</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>1 de 58</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
-        <is>
-          <t>5 de 58</t>
-        </is>
-      </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="O60" s="4" t="inlineStr">
-        <is>
-          <t>2 de 58</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
-        </is>
-      </c>
-      <c r="R60" s="4" t="inlineStr">
-        <is>
-          <t>0 de 58</t>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>1 de 57</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>1 de 57</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>1 de 57</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>1 de 57</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>4 de 57</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>1 de 57</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
+        </is>
+      </c>
+      <c r="R59" s="4" t="inlineStr">
+        <is>
+          <t>0 de 57</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5430,23 +5370,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RUALES SARAGURO JIMMY JAVIER</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>3130.46</v>
+        <v>0</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>765.08</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>8877.290000000001</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>3754.52</v>
+        <v>0</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5457,7 +5397,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -5484,7 +5424,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -5511,7 +5451,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
+          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -5538,17 +5478,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
+          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0</v>
+        <v>165.48</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>255.57</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0</v>
@@ -5565,23 +5505,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
+          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0</v>
+        <v>6889.32</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>165.48</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>255.57</v>
+        <v>0</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="54">
@@ -5592,11 +5532,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>6889.32</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0</v>
@@ -5608,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5619,7 +5559,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>SOPLIN MENDOZA TABITA</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -5646,7 +5586,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SOPLIN MENDOZA TABITA</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -5673,11 +5613,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
+          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0</v>
+        <v>269.28</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0</v>
@@ -5686,10 +5626,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58">
@@ -5700,67 +5640,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
+          <t>VIVANCO MALDONADO SILVANA MARILY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>269.28</v>
+        <v>1443.42</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0</v>
+        <v>1062.8</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0</v>
+        <v>673.6900000000001</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>24.88</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>VIVANCO MALDONADO SILVANA MARILY</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>1443.42</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>1062.8</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>673.6900000000001</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" s="6" t="n">
-        <v>53770.63</v>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>53165.42</v>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>57170.26</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>26277.17</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>47000</v>
+      <c r="C59" s="6" t="n">
+        <v>50640.17</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>52400.34</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>48292.97</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>22522.65</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>45000</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALTAMIRANO VILLAVICENCIO JUAN ALEJANDRO</t>
+          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14685.95</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>445.75</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0</v>
+        <v>796.95</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>364.5</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>3094.82</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1406,17 +1406,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>445.75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>796.95</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>364.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3094.82</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>24.48</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA RAMIREZ GALVAN CIA. LTDA</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIAZ CHAVEZ DIEGO FERNANDO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0</v>
+        <v>1694.28</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1694.28</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>JUAREZ FLORES JORGE WILLIAMS</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JUAREZ FLORES JORGE WILLIAMS</t>
+          <t>MENA COSTA GUIDO LENNIN</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>MORALES GRACIELA ENITH</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MENA COSTA GUIDO LENNIN</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MONTAÑO JIMENEZ SANDRA GABRIELA</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORALES GRACIELA ENITH</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
+          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PACHAR TAPIA ELIANA DE LOS ANGELES</t>
+          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QUIÑONEZ LEON MARIA PURIFICACION</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ROBLES CAMPOVERDE TANIA CRISTINA</t>
+          <t>SOPLIN MENDOZA TABITA</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>0</v>
@@ -3439,624 +3439,84 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SOPLIN MENDOZA TABITA</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>VIVANCO MALDONADO SILVANA MARILY</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>1 de 57</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>1 de 57</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>1 de 57</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>1 de 57</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>4 de 57</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="O59" s="4" t="inlineStr">
-        <is>
-          <t>1 de 57</t>
-        </is>
-      </c>
-      <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
-        </is>
-      </c>
-      <c r="R59" s="4" t="inlineStr">
-        <is>
-          <t>0 de 57</t>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>1 de 48</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>1 de 48</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>1 de 48</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>1 de 48</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>4 de 48</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>1 de 48</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>0 de 48</t>
         </is>
       </c>
     </row>
@@ -4071,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4182,17 +3642,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALTAMIRANO VILLAVICENCIO JUAN ALEJANDRO</t>
+          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>848.76</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>785.09</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>661.5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -4209,7 +3669,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -4219,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>661.5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -4236,23 +3696,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2637.26</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2633.88</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -4263,23 +3723,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2637.26</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2633.88</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4290,7 +3750,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -4306,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
@@ -4317,23 +3777,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>12084.08</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>25493.19</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>6961.7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10">
@@ -4344,23 +3804,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12084.08</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>25493.19</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6961.7</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>14685.95</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4371,7 +3831,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -4381,13 +3841,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>22326.23</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="12">
@@ -4398,7 +3858,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -4408,13 +3868,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>22326.23</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4425,7 +3885,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -4452,11 +3912,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>1445.41</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -4479,23 +3939,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1445.41</v>
+        <v>12247.2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>9080.27</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>352.8</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>6093.06</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -4506,23 +3966,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>12247.2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9080.27</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>352.8</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6093.06</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4533,7 +3993,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4546,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>24.48</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -4560,7 +4020,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA RAMIREZ GALVAN CIA. LTDA</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4587,7 +4047,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4600,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -4614,7 +4074,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -4641,7 +4101,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -4668,7 +4128,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIAZ CHAVEZ DIEGO FERNANDO</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -4684,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4695,7 +4155,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -4711,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="24">
@@ -4722,23 +4182,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>1891.36</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>1058.37</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
@@ -4749,7 +4209,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -4776,23 +4236,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>278.41</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>597.52</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>126.72</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27">
@@ -4803,17 +4263,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1891.36</v>
+        <v>4357.13</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1058.37</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -4830,11 +4290,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>89.56</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -4843,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>1694.28</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -4857,23 +4317,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>278.41</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>597.52</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.72</v>
+        <v>104.6</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4884,14 +4344,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4357.13</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0</v>
@@ -4900,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4911,11 +4371,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>89.56</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
@@ -4924,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1694.28</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -4938,17 +4398,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>JUAREZ FLORES JORGE WILLIAMS</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0</v>
+        <v>3066.76</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0</v>
+        <v>1770.09</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>104.6</v>
+        <v>381.6</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
@@ -4965,7 +4425,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -4992,7 +4452,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -5019,17 +4479,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JUAREZ FLORES JORGE WILLIAMS</t>
+          <t>MENA COSTA GUIDO LENNIN</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3066.76</v>
+        <v>0</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1770.09</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>381.6</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>0</v>
@@ -5046,7 +4506,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -5073,11 +4533,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>MORALES GRACIELA ENITH</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0</v>
+        <v>829.4400000000001</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0</v>
@@ -5100,7 +4560,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MENA COSTA GUIDO LENNIN</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -5110,13 +4570,13 @@
         <v>0</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>1351.92</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="39">
@@ -5127,7 +4587,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -5154,7 +4614,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MONTAÑO JIMENEZ SANDRA GABRIELA</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -5181,11 +4641,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORALES GRACIELA ENITH</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>829.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0</v>
@@ -5208,7 +4668,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -5218,13 +4678,13 @@
         <v>0</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1351.92</v>
+        <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5235,7 +4695,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
+          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -5262,17 +4722,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PACHAR TAPIA ELIANA DE LOS ANGELES</t>
+          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0</v>
+        <v>165.48</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0</v>
+        <v>255.57</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0</v>
@@ -5289,11 +4749,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0</v>
+        <v>6889.32</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0</v>
@@ -5305,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="46">
@@ -5316,7 +4776,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QUIÑONEZ LEON MARIA PURIFICACION</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -5343,14 +4803,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ROBLES CAMPOVERDE TANIA CRISTINA</t>
+          <t>SOPLIN MENDOZA TABITA</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3628.38</v>
+        <v>0</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2179.48</v>
+        <v>0</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
@@ -5359,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5370,7 +4830,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -5397,11 +4857,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0</v>
+        <v>269.28</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0</v>
@@ -5410,270 +4870,27 @@
         <v>0</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0</v>
+        <v>24.88</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ NILO GUILLERMO</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>165.48</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>255.57</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>6889.32</v>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SOPLIN MENDOZA TABITA</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>269.28</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>VIVANCO MALDONADO SILVANA MARILY</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>1443.42</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>1062.8</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>673.6900000000001</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" s="6" t="n">
-        <v>50640.17</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>52400.34</v>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>48292.97</v>
-      </c>
-      <c r="F59" s="6" t="n">
+      <c r="C50" s="6" t="n">
+        <v>44719.61</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>48372.97</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>47619.28</v>
+      </c>
+      <c r="F50" s="6" t="n">
         <v>22522.65</v>
       </c>
-      <c r="G59" s="6" t="n">
-        <v>45000</v>
+      <c r="G50" s="6" t="n">
+        <v>43000</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -626,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALTAMIRANO ARIAS LUCIA ELIZABETH</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -926,7 +926,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14685.95</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>445.75</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0</v>
+        <v>796.95</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>364.5</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>3094.82</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>445.75</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>796.95</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>364.5</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3094.82</v>
+        <v>24.48</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1500,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1694.28</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUAREZ FLORES JORGE WILLIAMS</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MENA COSTA GUIDO LENNIN</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2659,864 +2659,84 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>MORALES GRACIELA ENITH</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SOPLIN MENDOZA TABITA</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>1 de 48</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>1 de 48</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>1 de 48</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>1 de 48</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>4 de 48</t>
-        </is>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="O50" s="4" t="inlineStr">
-        <is>
-          <t>1 de 48</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
-        </is>
-      </c>
-      <c r="R50" s="4" t="inlineStr">
-        <is>
-          <t>0 de 48</t>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>3 de 35</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
         </is>
       </c>
     </row>
@@ -3531,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3615,23 +2835,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALTAMIRANO ARIAS LUCIA ELIZABETH</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6405.28</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>6526.56</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3642,23 +2862,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALVAREZ SAAVEDRA EDWIN GEOVANNY</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2637.26</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>661.5</v>
+        <v>2633.88</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -3669,7 +2889,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -3696,23 +2916,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2637.26</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2633.88</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
@@ -3723,23 +2943,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>12084.08</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>25493.19</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>6961.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>14685.95</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8">
@@ -3750,7 +2970,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -3766,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3777,23 +2997,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12084.08</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>25493.19</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6961.7</v>
+        <v>22326.23</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>14685.95</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="10">
@@ -3804,7 +3024,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3831,7 +3051,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -3841,13 +3061,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>22326.23</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3858,11 +3078,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>1445.41</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -3885,23 +3105,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>12247.2</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>9080.27</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>352.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>6093.06</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -3912,11 +3132,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1445.41</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -3939,23 +3159,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>12247.2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9080.27</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>352.8</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6093.06</v>
+        <v>24.48</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3966,7 +3186,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -3993,7 +3213,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4006,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -4020,7 +3240,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -4047,7 +3267,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -4074,7 +3294,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -4101,7 +3321,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -4117,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="22">
@@ -4128,7 +3348,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -4155,23 +3375,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>278.41</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>597.52</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>126.72</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
@@ -4182,17 +3402,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRANDA SANDOVAL JACKELINE ELIZABETH</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1891.36</v>
+        <v>4357.13</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1058.37</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -4209,7 +3429,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -4219,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>104.6</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
@@ -4236,23 +3456,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>278.41</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>597.52</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>126.72</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -4263,14 +3483,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>4357.13</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -4279,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4290,11 +3510,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IMPORTADORA ORTEGA CIA. LTDA.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>89.56</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -4303,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1694.28</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -4317,7 +3537,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -4327,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>104.6</v>
+        <v>0</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>0</v>
@@ -4344,7 +3564,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -4371,7 +3591,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -4381,13 +3601,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>1351.92</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32">
@@ -4398,17 +3618,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUAREZ FLORES JORGE WILLIAMS</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>3066.76</v>
+        <v>0</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1770.09</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>381.6</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
@@ -4425,7 +3645,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -4452,7 +3672,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -4479,7 +3699,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MENA COSTA GUIDO LENNIN</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -4506,7 +3726,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -4526,371 +3746,20 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>MORALES GRACIELA ENITH</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>829.4400000000001</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>1351.92</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ORTIZ GRANDA ANDREA DEL CISNE</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SANDOVAL GONZALEZ LAUTARO MARCELO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SARITAMA HERRERA MARIA ELIZABETH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>165.48</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>255.57</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SIMANCAS AGUILAR HONORIO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>6889.32</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SOPLIN MENDOZA TABITA</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>VEINTIMILLA JARAMILLO HERMANOS VJHNOS S.A.S.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>269.28</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="6" t="n">
-        <v>44719.61</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>48372.97</v>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>47619.28</v>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>22522.65</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>43000</v>
+      <c r="C37" s="6" t="n">
+        <v>27169.97</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>44546.04</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>38735.68</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>20803.49</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>35500</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>3 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24.48</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>20803.49</v>
+        <v>20779.01</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14685.95</v>
+        <v>22781.83</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>6961.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>14685.95</v>
+        <v>22781.83</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>20779.01</v>
+        <v>28874.89</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22781.83</v>
+        <v>22334.38</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>184.77</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0</v>
+        <v>409.98</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>3 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2956,7 +2956,7 @@
         <v>6961.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22781.83</v>
+        <v>22334.38</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>594.75</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>28874.89</v>
+        <v>29022.19</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3773,15 +3773,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3828,13 +3828,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>129.6</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3852,16 +3852,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1867.69</v>
+        <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3471.56</v>
+        <v>1391.04</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1603.87</v>
+        <v>122.96</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.858745294990068</v>
+        <v>0.9187846763540291</v>
       </c>
     </row>
     <row r="4">
@@ -3876,16 +3876,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1987.7</v>
+        <v>1620.15</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2172.1</v>
+        <v>445.75</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-184.3999999999999</v>
+        <v>1174.4</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.092770538813704</v>
+        <v>0.2751288460944974</v>
       </c>
     </row>
     <row r="5">
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>86.41</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3924,16 +3924,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1815</v>
+        <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>796.95</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1815</v>
+        <v>-236.95</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.423125</v>
       </c>
     </row>
     <row r="7">
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>383.4</v>
+        <v>916.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1748.16</v>
+        <v>364.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1364.76</v>
+        <v>552.15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4.55962441314554</v>
+        <v>0.3976435935198822</v>
       </c>
     </row>
     <row r="8">
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>415</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>29.49</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>385.51</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.07106024096385542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>388.107983534392</v>
+        <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3377.81</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-2989.702016465608</v>
+        <v>203.763</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8.703273684914231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4044,16 +4044,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1440.92</v>
+        <v>2105</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14407.86</v>
+        <v>438.21</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-12966.94</v>
+        <v>1666.79</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9.999070038586458</v>
+        <v>0.2081757719714964</v>
       </c>
     </row>
     <row r="12">
@@ -4068,16 +4068,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>48041</v>
+        <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>36359.92</v>
+        <v>27583.7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11681.08</v>
+        <v>9666.299999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.756851855706584</v>
+        <v>0.7405020134228188</v>
       </c>
     </row>
     <row r="13">
@@ -4092,35 +4092,59 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1332.52398144409</v>
+        <v>1198.8</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1332.52398144409</v>
+        <v>1198.8</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>3729.16</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>-3369.16</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>10.35877777777778</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>57887.35196497848</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>61566.89999999999</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-3679.548035021517</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.063563937719031</v>
+      <c r="C15" s="2" t="n">
+        <v>46287.26300000001</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>34749.31</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>11537.953</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.7507315781449422</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>1711.22</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>3 de 35</t>
+          <t>4 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2821,7 +2821,7 @@
         <v>4877.83</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1711.22</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>29022.19</v>
+        <v>30733.41</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3779,8 +3779,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4071,13 +4071,13 @@
         <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>27583.7</v>
+        <v>29294.92</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9666.299999999999</v>
+        <v>7955.080000000002</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7405020134228188</v>
+        <v>0.7864408053691274</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>46287.26300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>34749.31</v>
+        <v>36460.53</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11537.953</v>
+        <v>9826.733</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7507315781449422</v>
+        <v>0.7877011436169815</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3094.82</v>
+        <v>4322.98</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>352.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6093.06</v>
+        <v>7321.22</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>30733.41</v>
+        <v>31961.57</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -4071,13 +4071,13 @@
         <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>29294.92</v>
+        <v>30523.08</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7955.080000000002</v>
+        <v>6726.919999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7864408053691274</v>
+        <v>0.8194115436241611</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>46287.26300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>36460.53</v>
+        <v>37688.69</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9826.733</v>
+        <v>8598.572999999997</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7877011436169815</v>
+        <v>0.8142345767992374</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>29.44</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>4 de 35</t>
+          <t>5 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>29.44</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>31961.57</v>
+        <v>31991.01</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3780,7 +3780,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4071,13 +4071,13 @@
         <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30523.08</v>
+        <v>30552.52</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6726.919999999998</v>
+        <v>6697.48</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8194115436241611</v>
+        <v>0.8202018791946308</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>46287.26300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>37688.69</v>
+        <v>37718.13</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8598.572999999997</v>
+        <v>8569.132999999998</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8142345767992374</v>
+        <v>0.8148706049005316</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3780,7 +3780,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4071,13 +4071,13 @@
         <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30552.52</v>
+        <v>30581.96</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6697.48</v>
+        <v>6668.040000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8202018791946308</v>
+        <v>0.8209922147651006</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>46287.26300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>37718.13</v>
+        <v>37747.56999999999</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8569.132999999998</v>
+        <v>8539.692999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8148706049005316</v>
+        <v>0.8155066330018257</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4071,13 +4071,13 @@
         <v>37250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30581.96</v>
+        <v>30470.08</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6668.040000000001</v>
+        <v>6779.919999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8209922147651006</v>
+        <v>0.8179887248322149</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>46287.26300000001</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>37747.56999999999</v>
+        <v>37635.69</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8539.692999999999</v>
+        <v>8651.572999999997</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.8155066330018257</v>
+        <v>0.8130895533831844</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3773,7 +3773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4040,20 +4040,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2105</v>
+        <v>460</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>438.21</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1666.79</v>
+        <v>460</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2081757719714964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4064,20 +4064,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>37250</v>
+        <v>2105</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30470.08</v>
+        <v>438.21</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6779.919999999998</v>
+        <v>1666.79</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8179887248322149</v>
+        <v>0.2081757719714964</v>
       </c>
     </row>
     <row r="13">
@@ -4088,20 +4088,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1198.8</v>
+        <v>37250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>30470.08</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1198.8</v>
+        <v>6779.919999999998</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.8179887248322149</v>
       </c>
     </row>
     <row r="14">
@@ -4112,39 +4112,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>PUERTAS DE SEGURIDAD</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>SAL SOLUBLE</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>3729.16</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>-3369.16</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>10.35877777777778</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>46287.26300000001</v>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C16" s="2" t="n">
+        <v>46747.26300000001</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>37635.69</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>8651.572999999997</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.8130895533831844</v>
+      <c r="E16" s="2" t="n">
+        <v>9111.572999999997</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.8050886316060899</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>1902.56</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>29.44</v>
+        <v>1932</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>31991.01</v>
+        <v>33893.57000000001</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3951,13 +3951,13 @@
         <v>916.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>364.5</v>
+        <v>2267.06</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>552.15</v>
+        <v>-1350.41</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3976435935198822</v>
+        <v>2.47320133093329</v>
       </c>
     </row>
     <row r="8">
@@ -4162,13 +4162,13 @@
         <v>46747.26300000001</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>37635.69</v>
+        <v>39538.25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>9111.572999999997</v>
+        <v>7209.012999999997</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8050886316060899</v>
+        <v>0.8457874849271924</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>14.76</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>5 de 35</t>
+          <t>6 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
         <v>126.72</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>14.76</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>33893.57000000001</v>
+        <v>33908.33</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3780,7 +3780,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4095,13 +4095,13 @@
         <v>37250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30470.08</v>
+        <v>30484.84</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6779.919999999998</v>
+        <v>6765.16</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8179887248322149</v>
+        <v>0.818384966442953</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>46747.26300000001</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39538.25</v>
+        <v>39553.00999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7209.012999999997</v>
+        <v>7194.252999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8457874849271924</v>
+        <v>0.8461032253374917</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>380.16</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1711.22</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>897.6</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22334.38</v>
+        <v>22293.34</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -2821,7 +2821,7 @@
         <v>4877.83</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1711.22</v>
+        <v>2091.38</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -2929,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>897.6</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1500</v>
@@ -2956,7 +2956,7 @@
         <v>6961.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22334.38</v>
+        <v>22293.34</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>33908.33</v>
+        <v>35145.05</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3779,8 +3779,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3927,13 +3927,13 @@
         <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>796.95</v>
+        <v>1694.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-236.95</v>
+        <v>-1134.55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.423125</v>
+        <v>3.025982142857143</v>
       </c>
     </row>
     <row r="7">
@@ -4071,13 +4071,13 @@
         <v>2105</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>438.21</v>
+        <v>818.37</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1666.79</v>
+        <v>1286.63</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2081757719714964</v>
+        <v>0.3887743467933492</v>
       </c>
     </row>
     <row r="13">
@@ -4095,13 +4095,13 @@
         <v>37250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30484.84</v>
+        <v>30443.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6765.16</v>
+        <v>6806.200000000001</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.818384966442953</v>
+        <v>0.81728322147651</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>46747.26300000001</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>39553.00999999999</v>
+        <v>40789.73</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7194.252999999999</v>
+        <v>5957.533000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8461032253374917</v>
+        <v>0.8725586779273043</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>380.16</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1711.22</v>
+        <v>1639.92</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>4877.83</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2091.38</v>
+        <v>2020.08</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>38735.68</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>35145.05</v>
+        <v>35073.75000000001</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3780,7 +3780,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4095,13 +4095,13 @@
         <v>37250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30443.8</v>
+        <v>30372.5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6806.200000000001</v>
+        <v>6877.5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.81728322147651</v>
+        <v>0.8153691275167785</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>46747.26300000001</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>40789.73</v>
+        <v>40718.42999999999</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5957.533000000001</v>
+        <v>6028.832999999999</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8725586779273043</v>
+        <v>0.8710334549425918</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,10 +597,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>380.16</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1639.92</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>897.6</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22293.34</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1233,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>445.75</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>796.95</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>364.5</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4322.98</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1902.56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>29.44</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>14.76</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>184.77</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>409.98</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>6 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2756,10 +2756,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2776,22 +2776,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2812,16 +2812,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1114.87</v>
+        <v>2380.67</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2380.67</v>
+        <v>4877.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4877.83</v>
+        <v>2020.08</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2020.08</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>2637.26</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2637.26</v>
+        <v>2633.88</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2633.88</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>897.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>897.6</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1500</v>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12084.08</v>
+        <v>25493.19</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>25493.19</v>
+        <v>6961.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6961.7</v>
+        <v>22293.34</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22293.34</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3004,10 +3004,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>22326.23</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>22326.23</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1445.41</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>12247.2</v>
+        <v>9080.27</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9080.27</v>
+        <v>352.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>352.8</v>
+        <v>7321.22</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7321.22</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3331,10 +3331,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1932</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3379,16 +3379,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>278.41</v>
+        <v>597.52</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>597.52</v>
+        <v>126.72</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>126.72</v>
+        <v>14.76</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>14.76</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>4357.13</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4357.13</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>104.6</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>104.6</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>594.75</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>594.75</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0</v>
@@ -3598,10 +3598,10 @@
         <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>1351.92</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1351.92</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="37">
       <c r="C37" s="6" t="n">
-        <v>27169.97</v>
+        <v>44546.04</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>44546.04</v>
+        <v>38735.68</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>38735.68</v>
+        <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>35073.75000000001</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>5037.12</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2601.72</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2666,52 +2666,52 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>7638.84</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3334,7 +3334,7 @@
         <v>1932</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>7665.84</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3781,7 +3781,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1391.04</v>
+        <v>5037.12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>122.96</v>
+        <v>-3523.12</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.9187846763540291</v>
+        <v>3.327027741083223</v>
       </c>
     </row>
     <row r="4">
@@ -3876,16 +3876,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1620.15</v>
+        <v>620</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>445.75</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1174.4</v>
+        <v>620</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2751288460944974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3927,13 +3927,13 @@
         <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1694.55</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1134.55</v>
+        <v>560</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.025982142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3951,13 +3951,13 @@
         <v>916.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2267.06</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1350.41</v>
+        <v>916.65</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.47320133093329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4071,13 +4071,13 @@
         <v>2105</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>818.37</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1286.63</v>
+        <v>2105</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.3887743467933492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4092,16 +4092,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>37250</v>
+        <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>30372.5</v>
+        <v>2628.72</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6877.5</v>
+        <v>32621.28</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8153691275167785</v>
+        <v>0.07457361702127659</v>
       </c>
     </row>
     <row r="14">
@@ -4143,13 +4143,13 @@
         <v>360</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3729.16</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-3369.16</v>
+        <v>360</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>10.35877777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46747.26300000001</v>
+        <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>40718.42999999999</v>
+        <v>7665.84</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6028.832999999999</v>
+        <v>36081.273</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8710334549425918</v>
+        <v>0.1752307632277357</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5037.12</v>
+        <v>8700.48</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2601.72</v>
+        <v>7924.3</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7638.84</v>
+        <v>16624.78</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>7665.84</v>
+        <v>16651.78</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3781,7 +3781,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5037.12</v>
+        <v>8700.48</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3523.12</v>
+        <v>-7186.48</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.327027741083223</v>
+        <v>5.74668428005284</v>
       </c>
     </row>
     <row r="4">
@@ -4095,13 +4095,13 @@
         <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2628.72</v>
+        <v>7951.3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>32621.28</v>
+        <v>27298.7</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.07457361702127659</v>
+        <v>0.2255687943262411</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7665.84</v>
+        <v>16651.78</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>36081.273</v>
+        <v>27095.333</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1752307632277357</v>
+        <v>0.380637231992886</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>3038.61</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>3 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3118,7 +3118,7 @@
         <v>7321.22</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>3038.61</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>16651.78</v>
+        <v>19690.39</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3779,7 +3779,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4095,13 +4095,13 @@
         <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7951.3</v>
+        <v>10989.91</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>27298.7</v>
+        <v>24260.09</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2255687943262411</v>
+        <v>0.3117704964539007</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>16651.78</v>
+        <v>19690.39</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>27095.333</v>
+        <v>24056.723</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.380637231992886</v>
+        <v>0.4500957583189546</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7924.3</v>
+        <v>7893.38</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3038.61</v>
+        <v>3033.21</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>16624.78</v>
+        <v>16593.86</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3118,7 +3118,7 @@
         <v>7321.22</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3038.61</v>
+        <v>3033.21</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>19690.39</v>
+        <v>19654.07</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -4095,13 +4095,13 @@
         <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10989.91</v>
+        <v>10953.59</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24260.09</v>
+        <v>24296.41</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3117704964539007</v>
+        <v>0.3107401418439716</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>19690.39</v>
+        <v>19654.07</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24056.723</v>
+        <v>24093.043</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4500957583189546</v>
+        <v>0.4492655321049414</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>282.62</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
         <v>14.76</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>282.62</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>19654.07</v>
+        <v>19936.69</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -4071,13 +4071,13 @@
         <v>2105</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>282.62</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2105</v>
+        <v>1822.38</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.1342612826603325</v>
       </c>
     </row>
     <row r="13">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>19654.07</v>
+        <v>19936.69</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>24093.043</v>
+        <v>23810.423</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4492655321049414</v>
+        <v>0.4557258441259884</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -813,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2324.16</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -825,22 +825,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>1027.95</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>153.12</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>609.12</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>748.36</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>839.3</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2666,42 +2666,42 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>2 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>1 de 35</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>3 de 35</t>
+          <t>4 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2929,7 +2929,7 @@
         <v>897.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>5567.77</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1500</v>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>839.3</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>500</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>19936.69</v>
+        <v>26343.76</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3780,7 +3780,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8700.48</v>
+        <v>11024.64</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-7186.48</v>
+        <v>-9510.639999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5.74668428005284</v>
+        <v>7.281796565389696</v>
       </c>
     </row>
     <row r="4">
@@ -3879,13 +3879,13 @@
         <v>620</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>705.0599999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>620</v>
+        <v>-85.05999999999995</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1.137193548387097</v>
       </c>
     </row>
     <row r="5">
@@ -3927,13 +3927,13 @@
         <v>560</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1027.95</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>560</v>
+        <v>-467.95</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.835625</v>
       </c>
     </row>
     <row r="7">
@@ -3951,13 +3951,13 @@
         <v>916.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>153.12</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>916.65</v>
+        <v>763.53</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.1670430371461299</v>
       </c>
     </row>
     <row r="8">
@@ -4023,13 +4023,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1448.42</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>203.763</v>
+        <v>-1244.657</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>7.108356276654741</v>
       </c>
     </row>
     <row r="11">
@@ -4095,13 +4095,13 @@
         <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>10953.59</v>
+        <v>11701.95</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24296.41</v>
+        <v>23548.05</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3107401418439716</v>
+        <v>0.3319702127659575</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>19936.69</v>
+        <v>26343.76</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>23810.423</v>
+        <v>17403.353</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4557258441259884</v>
+        <v>0.6021828228985076</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -828,13 +828,13 @@
         <v>1027.95</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>153.12</v>
+        <v>127.6</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>609.12</v>
+        <v>553.28</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>897.6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5567.77</v>
+        <v>5486.41</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1500</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>26343.76</v>
+        <v>26262.4</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3951,13 +3951,13 @@
         <v>916.65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>153.12</v>
+        <v>127.6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>763.53</v>
+        <v>789.05</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1670430371461299</v>
+        <v>0.1392025309551083</v>
       </c>
     </row>
     <row r="8">
@@ -4023,13 +4023,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1448.42</v>
+        <v>1392.58</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1244.657</v>
+        <v>-1188.817</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>7.108356276654741</v>
+        <v>6.834312411968806</v>
       </c>
     </row>
     <row r="11">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>26343.76</v>
+        <v>26262.4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17403.353</v>
+        <v>17484.713</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6021828228985076</v>
+        <v>0.6003230430314338</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0</v>
+        <v>677.78</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>16593.86</v>
+        <v>17271.64</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>26262.4</v>
+        <v>26940.18</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3975,13 +3975,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>677.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>-427.78</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>2.71112</v>
       </c>
     </row>
     <row r="9">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>26262.4</v>
+        <v>26940.18</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17484.713</v>
+        <v>16806.933</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6003230430314338</v>
+        <v>0.6158161796871029</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2403.36</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>1667.94</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -2666,52 +2666,52 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>3 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
           <t>2 de 35</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>1 de 35</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>2 de 35</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>4 de 35</t>
+          <t>5 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>4071.3</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>35073.75000000001</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>26940.18</v>
+        <v>31011.48</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11024.64</v>
+        <v>13428</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-9510.639999999999</v>
+        <v>-11914</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>7.281796565389696</v>
+        <v>8.869220607661823</v>
       </c>
     </row>
     <row r="4">
@@ -4095,13 +4095,13 @@
         <v>35250</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11701.95</v>
+        <v>13369.89</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23548.05</v>
+        <v>21880.11</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3319702127659575</v>
+        <v>0.3792876595744681</v>
       </c>
     </row>
     <row r="14">
@@ -4162,13 +4162,13 @@
         <v>43747.113</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>26940.18</v>
+        <v>31011.48</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16806.933</v>
+        <v>12735.633</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.6158161796871029</v>
+        <v>0.7088806065899708</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2403.36</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1667.94</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2324.16</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>705.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -825,22 +825,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1027.95</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>127.6</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>553.28</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>748.36</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8700.48</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7893.38</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>677.78</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3033.21</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>3 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>5 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -2757,9 +2757,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="76" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2776,22 +2776,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2380.67</v>
+        <v>4877.83</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4877.83</v>
+        <v>2020.08</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2020.08</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2637.26</v>
+        <v>2633.88</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2633.88</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>4071.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4071.3</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1000</v>
@@ -2923,13 +2923,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>897.6</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>897.6</v>
+        <v>5486.41</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5486.41</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1500</v>
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>25493.19</v>
+        <v>6961.7</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6961.7</v>
+        <v>22293.34</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22293.34</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>22326.23</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>22326.23</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>17271.64</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>17271.64</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>9080.27</v>
+        <v>352.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>352.8</v>
+        <v>7321.22</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7321.22</v>
+        <v>3033.21</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3033.21</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3328,13 +3328,13 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1932</v>
+        <v>27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3379,16 +3379,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>597.52</v>
+        <v>126.72</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>126.72</v>
+        <v>14.76</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>14.76</v>
+        <v>282.62</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1000</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4357.13</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>104.6</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>104.6</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -3517,10 +3517,10 @@
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>594.75</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>594.75</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
@@ -3595,16 +3595,16 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>1351.92</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1351.92</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>839.3</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>500</v>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="37">
       <c r="C37" s="6" t="n">
-        <v>44546.04</v>
+        <v>38735.68</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>38735.68</v>
+        <v>35073.75000000001</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>35073.75000000001</v>
+        <v>31011.48</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>31011.48</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2751,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2760,7 +2760,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2794,11 +2793,6 @@
           <t>marzo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2823,9 +2817,6 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2850,9 +2841,6 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2877,9 +2865,6 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2904,9 +2889,6 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2931,9 +2913,6 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>1500</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2958,9 +2937,6 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>10000</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2985,9 +2961,6 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3012,9 +2985,6 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>14000</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3039,9 +3009,6 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3066,9 +3033,6 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3093,9 +3057,6 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3120,9 +3081,6 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3147,9 +3105,6 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3174,9 +3129,6 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3201,9 +3153,6 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3228,9 +3177,6 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3255,9 +3201,6 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3282,9 +3225,6 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3309,9 +3249,6 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3336,9 +3273,6 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>2500</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3363,9 +3297,6 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3390,9 +3321,6 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3417,9 +3345,6 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3444,9 +3369,6 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3471,9 +3393,6 @@
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3498,9 +3417,6 @@
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3525,9 +3441,6 @@
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3552,9 +3465,6 @@
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3579,9 +3489,6 @@
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3606,9 +3513,6 @@
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>500</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3633,9 +3537,6 @@
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3660,9 +3561,6 @@
       <c r="F33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3687,9 +3585,6 @@
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3714,9 +3609,6 @@
       <c r="F35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3739,9 +3631,6 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3757,9 +3646,6 @@
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>35500</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2751,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2760,6 +2760,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2793,6 +2794,11 @@
           <t>marzo</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2817,6 +2823,9 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2841,6 +2850,9 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2865,6 +2877,9 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2889,6 +2904,9 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2913,6 +2931,9 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2937,6 +2958,9 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>10000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2961,6 +2985,9 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2985,6 +3012,9 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>14000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3009,6 +3039,9 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3033,6 +3066,9 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3057,6 +3093,9 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3081,6 +3120,9 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3105,6 +3147,9 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3129,6 +3174,9 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3153,6 +3201,9 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3177,6 +3228,9 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3201,6 +3255,9 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3225,6 +3282,9 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3249,6 +3309,9 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3273,6 +3336,9 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3297,6 +3363,9 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3321,6 +3390,9 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3345,6 +3417,9 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3369,6 +3444,9 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3393,6 +3471,9 @@
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3417,6 +3498,9 @@
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3441,6 +3525,9 @@
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3465,6 +3552,9 @@
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3489,6 +3579,9 @@
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3513,6 +3606,9 @@
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3537,6 +3633,9 @@
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3561,6 +3660,9 @@
       <c r="F33" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3585,6 +3687,9 @@
       <c r="F34" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3609,6 +3714,9 @@
       <c r="F35" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3631,6 +3739,9 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3646,6 +3757,9 @@
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>35500</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3773,15 +3773,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>13428</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-11914</v>
+        <v>1514</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8.869220607661823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3876,16 +3876,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>620</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>705.0599999999999</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-85.05999999999995</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.137193548387097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3924,16 +3924,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>560</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1027.95</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-467.95</v>
+        <v>240</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.835625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3948,16 +3948,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>916.65</v>
+        <v>263</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>127.6</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>789.05</v>
+        <v>263</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1392025309551083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3975,13 +3975,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>677.78</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-427.78</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2.71112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4023,13 +4023,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1392.58</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1188.817</v>
+        <v>203.763</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>6.834312411968806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>460</v>
+        <v>350</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>460</v>
+        <v>350</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -4068,16 +4068,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2105</v>
+        <v>1600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1822.38</v>
+        <v>1600</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1342612826603325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4092,16 +4092,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>35250</v>
+        <v>29057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13369.89</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>21880.11</v>
+        <v>29057</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3792876595744681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4129,46 +4129,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>360</v>
+        <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>360</v>
+        <v>35184.963</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>43747.113</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>31011.48</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>12735.633</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.7088806065899708</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3779,7 +3779,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4071,13 +4071,13 @@
         <v>1600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>-253.02</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1600</v>
+        <v>1853.02</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.1581375</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>-253.02</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>35184.963</v>
+        <v>35437.983</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>-0.007191140146999728</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,10 +597,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>380.16</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>2281.62</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>2661.78</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>31011.48</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>2661.78</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3781,7 +3781,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4071,13 +4071,13 @@
         <v>1600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>-253.02</v>
+        <v>127.14</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1853.02</v>
+        <v>1472.86</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>-0.1581375</v>
+        <v>0.07946250000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4095,13 +4095,13 @@
         <v>29057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>2281.62</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29057</v>
+        <v>26775.38</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.07852221495680903</v>
       </c>
     </row>
     <row r="14">
@@ -4138,13 +4138,13 @@
         <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>-253.02</v>
+        <v>2408.76</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>35437.983</v>
+        <v>32776.203</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-0.007191140146999728</v>
+        <v>0.0684599270432656</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>380.16</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2281.62</v>
+        <v>2263.79</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2661.78</v>
+        <v>2643.95</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>31011.48</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2661.78</v>
+        <v>2643.95</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3781,7 +3781,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4095,13 +4095,13 @@
         <v>29057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2281.62</v>
+        <v>2263.79</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26775.38</v>
+        <v>26793.21</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.07852221495680903</v>
+        <v>0.0779085934542451</v>
       </c>
     </row>
     <row r="14">
@@ -4138,13 +4138,13 @@
         <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2408.76</v>
+        <v>2390.93</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32776.203</v>
+        <v>32794.033</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.0684599270432656</v>
+        <v>0.06795317647484807</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3334,7 +3334,7 @@
         <v>27</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>133.81</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3756,7 +3756,7 @@
         <v>31011.48</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2643.95</v>
+        <v>2777.76</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -4047,13 +4047,13 @@
         <v>350</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>133.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>350</v>
+        <v>216.19</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.3823142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -4138,13 +4138,13 @@
         <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2390.93</v>
+        <v>2524.74</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32794.033</v>
+        <v>32660.223</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.06795317647484807</v>
+        <v>0.07175622154270844</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>1222.04</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0</v>
+        <v>153.76</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>479.4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>3400.15</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>4277.14</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2701,32 +2701,32 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>4 de 35</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>0 de 35</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -2875,7 +2875,7 @@
         <v>4071.3</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>1375.8</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1000</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>2375.07</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3010,7 +3010,7 @@
         <v>17271.64</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>3400.15</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3118,7 +3118,7 @@
         <v>3033.21</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>4277.14</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3756,7 +3756,7 @@
         <v>31011.48</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>2777.76</v>
+        <v>14205.92</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3779,8 +3779,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3975,13 +3975,13 @@
         <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>153.76</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>96.24000000000001</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>0.6150399999999999</v>
       </c>
     </row>
     <row r="9">
@@ -4023,13 +4023,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>479.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>203.763</v>
+        <v>-275.6369999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>2.352733322536476</v>
       </c>
     </row>
     <row r="11">
@@ -4047,13 +4047,13 @@
         <v>350</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>133.81</v>
+        <v>2029.48</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>216.19</v>
+        <v>-1679.48</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.3823142857142857</v>
+        <v>5.798514285714286</v>
       </c>
     </row>
     <row r="12">
@@ -4095,13 +4095,13 @@
         <v>29057</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2263.79</v>
+        <v>11163.12</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>26793.21</v>
+        <v>17893.88</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.0779085934542451</v>
+        <v>0.3841800598823003</v>
       </c>
     </row>
     <row r="14">
@@ -4138,13 +4138,13 @@
         <v>35184.963</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2524.74</v>
+        <v>13952.9</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32660.223</v>
+        <v>21232.063</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.07175622154270844</v>
+        <v>0.3965586094264189</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,10 +597,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>380.16</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2263.79</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1222.04</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>153.76</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>479.4</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3400.15</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4277.14</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>4 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -2756,10 +2756,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2776,22 +2776,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2812,16 +2812,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4877.83</v>
+        <v>2020.08</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2020.08</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>2643.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2643.95</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2633.88</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>4071.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4071.3</v>
+        <v>1375.8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1000</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>897.6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>897.6</v>
+        <v>5486.41</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5486.41</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6961.7</v>
+        <v>22293.34</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>22293.34</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2375.07</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2375.07</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>22326.23</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>17271.64</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17271.64</v>
+        <v>3400.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3400.15</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>14000</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>352.8</v>
+        <v>7321.22</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>7321.22</v>
+        <v>3033.21</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3033.21</v>
+        <v>4406.39</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4277.14</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1000</v>
@@ -3325,16 +3325,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>1932</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1932</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>27</v>
+        <v>133.81</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>133.81</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2500</v>
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>126.72</v>
+        <v>14.76</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>14.76</v>
+        <v>282.62</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>104.6</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>594.75</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>594.75</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1351.92</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>839.3</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="37">
       <c r="C37" s="6" t="n">
-        <v>38735.68</v>
+        <v>35073.75000000001</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>35073.75000000001</v>
+        <v>31011.48</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>31011.48</v>
+        <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14205.92</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>1071.13</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2821,7 +2821,7 @@
         <v>2643.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1071.13</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>1071.13</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3779,8 +3779,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3828,13 +3828,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>136.08</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>136.08</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -3920,17 +3920,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>240</v>
+        <v>347.55</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>240</v>
+        <v>347.55</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -3944,17 +3944,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -3968,20 +3968,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>153.76</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>96.24000000000001</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.6150399999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -4016,20 +4016,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>203.763</v>
+        <v>460</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>479.4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-275.6369999999999</v>
+        <v>460</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2.352733322536476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4040,20 +4040,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>350</v>
+        <v>2105</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2029.48</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1679.48</v>
+        <v>2105</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>5.798514285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4064,20 +4064,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1600</v>
+        <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>127.14</v>
+        <v>1071.13</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1472.86</v>
+        <v>24178.87</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.07946250000000001</v>
+        <v>0.0424209900990099</v>
       </c>
     </row>
     <row r="13">
@@ -4088,20 +4088,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>29057</v>
+        <v>327.6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11163.12</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17893.88</v>
+        <v>327.6</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3841800598823003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4112,17 +4112,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+          <t>SAL SOLUBLE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1198.8</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1198.8</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -4135,16 +4135,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>35184.963</v>
+        <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13952.9</v>
+        <v>1071.13</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21232.063</v>
+        <v>29759.103</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.3965586094264189</v>
+        <v>0.03474284479134492</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1071.13</v>
+        <v>1035.88</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>2643.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1071.13</v>
+        <v>1035.88</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -2956,7 +2956,7 @@
         <v>2375.07</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>-84.25</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10000</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1071.13</v>
+        <v>951.6300000000001</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>35500</v>
@@ -3781,7 +3781,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4023,13 +4023,13 @@
         <v>460</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>-84.25</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>460</v>
+        <v>544.25</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>-0.1831521739130435</v>
       </c>
     </row>
     <row r="11">
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1071.13</v>
+        <v>1035.88</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24178.87</v>
+        <v>24214.12</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.0424209900990099</v>
+        <v>0.04102495049504951</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1071.13</v>
+        <v>951.6300000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29759.103</v>
+        <v>29878.603</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.03474284479134492</v>
+        <v>0.0308667793720534</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2959,7 +2959,7 @@
         <v>-84.25</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3391,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3759,7 +3759,7 @@
         <v>951.6300000000001</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>35500</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>3812.32</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>3069.67</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2666,52 +2666,52 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>3400.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>6881.99</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>951.6300000000001</v>
+        <v>7833.62</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -3855,13 +3855,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>3812.32</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1514</v>
+        <v>-2298.32</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>2.518044914134742</v>
       </c>
     </row>
     <row r="4">
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1035.88</v>
+        <v>4105.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24214.12</v>
+        <v>21144.45</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.04102495049504951</v>
+        <v>0.1625960396039604</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>951.6300000000001</v>
+        <v>7833.620000000001</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29878.603</v>
+        <v>22996.613</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.0308667793720534</v>
+        <v>0.2540889003336433</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>-59.4</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>2643.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1035.88</v>
+        <v>976.48</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>7833.62</v>
+        <v>7774.219999999999</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -3927,13 +3927,13 @@
         <v>347.55</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>-59.4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>347.55</v>
+        <v>406.95</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>-0.1709106603366422</v>
       </c>
     </row>
     <row r="7">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7833.620000000001</v>
+        <v>7774.22</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>22996.613</v>
+        <v>23056.013</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2540889003336433</v>
+        <v>0.2521622201168574</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>685.84</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>5802.81</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>2 de 35</t>
+          <t>3 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
         <v>133.81</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>6488.65</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>7774.219999999999</v>
+        <v>14262.87</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -4047,13 +4047,13 @@
         <v>2105</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>685.84</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2105</v>
+        <v>1419.16</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.3258147268408551</v>
       </c>
     </row>
     <row r="12">
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4105.55</v>
+        <v>9908.360000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21144.45</v>
+        <v>15341.64</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1625960396039604</v>
+        <v>0.392410297029703</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7774.22</v>
+        <v>14262.87</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>23056.013</v>
+        <v>16567.363</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2521622201168574</v>
+        <v>0.4626260852456094</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>959.02</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3069.67</v>
+        <v>3931.37</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2956,7 +2956,7 @@
         <v>2375.07</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-84.25</v>
+        <v>874.77</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>3400.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6881.99</v>
+        <v>7743.69</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14262.87</v>
+        <v>16083.59</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -3779,7 +3779,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3879,13 +3879,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>959.02</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>-759.52</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>4.807117794486215</v>
       </c>
     </row>
     <row r="5">
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9908.360000000001</v>
+        <v>10770.06</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15341.64</v>
+        <v>14479.94</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.392410297029703</v>
+        <v>0.4265370297029702</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14262.87</v>
+        <v>16083.59</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16567.363</v>
+        <v>14746.643</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.4626260852456094</v>
+        <v>0.5216824018164248</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1740,7 +1740,7 @@
         <v>685.84</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5802.81</v>
+        <v>5735.46</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -3334,7 +3334,7 @@
         <v>133.81</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6488.65</v>
+        <v>6421.3</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>16083.59</v>
+        <v>16016.24</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10770.06</v>
+        <v>10702.71</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14479.94</v>
+        <v>14547.29</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.4265370297029702</v>
+        <v>0.423869702970297</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16083.59</v>
+        <v>16016.24</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14746.643</v>
+        <v>14813.993</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5216824018164248</v>
+        <v>0.5194978578332509</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1740,7 +1740,7 @@
         <v>685.84</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5735.46</v>
+        <v>9611.620000000001</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3334,7 +3334,7 @@
         <v>133.81</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6421.3</v>
+        <v>10297.46</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>14335.17</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>16016.24</v>
+        <v>19892.4</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>
@@ -4071,13 +4071,13 @@
         <v>25250</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10702.71</v>
+        <v>14578.87</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14547.29</v>
+        <v>10671.13</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.423869702970297</v>
+        <v>0.5773809900990099</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4138,13 @@
         <v>30830.233</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>16016.24</v>
+        <v>19892.4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14813.993</v>
+        <v>10937.833</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5194978578332509</v>
+        <v>0.6452237970436357</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-59.4</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1035.88</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>959.02</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3812.32</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3931.37</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1737,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>685.84</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9611.620000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>3 de 35</t>
+          <t>0 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2757,9 +2757,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="76" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2776,22 +2776,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2812,16 +2812,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2020.08</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2643.95</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2643.95</v>
+        <v>976.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>976.48</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>2000</v>
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>4071.3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4071.3</v>
+        <v>1375.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>897.6</v>
+        <v>5486.41</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5486.41</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22293.34</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>2375.07</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2375.07</v>
+        <v>874.77</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>874.77</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>17271.64</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17271.64</v>
+        <v>3400.15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3400.15</v>
+        <v>7743.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7743.69</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7321.22</v>
+        <v>3033.21</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>3033.21</v>
+        <v>4406.39</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4406.39</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -3325,16 +3325,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1932</v>
+        <v>27</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>27</v>
+        <v>133.81</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>133.81</v>
+        <v>10297.46</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>10297.46</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14.76</v>
+        <v>282.62</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>594.75</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>839.3</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -3747,16 +3747,16 @@
     </row>
     <row r="37">
       <c r="C37" s="6" t="n">
-        <v>35073.75000000001</v>
+        <v>31011.48</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>31011.48</v>
+        <v>14335.17</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>14335.17</v>
+        <v>19892.4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>19892.4</v>
+        <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>1306.37</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>6387.62</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>6259.72</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2666,52 +2666,52 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
+          <t>1 de 35</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>0 de 35</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>2 de 35</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3010,7 +3010,7 @@
         <v>7743.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>7693.99</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>6259.72</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>19892.4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0</v>
+        <v>13953.71</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>124.64</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>0 de 35</t>
+          <t>1 de 35</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>145.7</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>19892.4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>13953.71</v>
+        <v>14099.41</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6387.62</v>
+        <v>6368.04</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>7743.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7693.99</v>
+        <v>7674.41</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>19892.4</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14099.41</v>
+        <v>14079.83</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2751,7 +2751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2808,23 +2808,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALARCON MAYORGA LUIS ALFONSO</t>
+          <t>AJILA CRUZ JOSE CHI</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2643.95</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>976.48</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2835,23 +2835,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ALARCON MAYORGA LUIS ALFONSO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2643.95</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>976.48</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -2862,14 +2862,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4071.3</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
@@ -2889,14 +2889,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>4071.3</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1375.8</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -2916,11 +2916,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5486.41</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2943,17 +2943,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>5486.41</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2375.07</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>874.77</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>BARRETO CHAVARRIA RENZO DUVAL</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>17271.64</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3400.15</v>
+        <v>2375.07</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7743.69</v>
+        <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7674.41</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3051,20 +3051,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>17271.64</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>3400.15</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0</v>
+        <v>7743.69</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>7674.41</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -3105,20 +3105,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>3033.21</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4406.39</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6259.72</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -3159,20 +3159,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>3033.21</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>4406.39</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>6259.72</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -3213,14 +3213,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>-253.02</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>133.81</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10297.46</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -3375,11 +3375,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>145.7</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3402,17 +3402,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>133.81</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>10297.46</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>FULLCONSTRU S.A.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3483,11 +3483,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>282.62</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>145.7</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3591,11 +3591,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>INTROMEX S.A.</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>LIBERIO SUAREZ PEDRO ADAN</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3726,39 +3726,417 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>LUI WONG ANGEL BOLIVAR</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MEJIA FERRIN HOLGER EDEN</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MINUTOCORP S.A.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>839.3</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MUÑOZ FALCONEZ SIGIFREDO DOMINGO</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PROAÑO CELA BLANCA LUCILA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>REYES GUILLEN VICTOR EUGENIO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="6" t="n">
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TORRES KUON YENG LETICIA AMERICA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="6" t="n">
         <v>31011.48</v>
       </c>
-      <c r="D37" s="6" t="n">
-        <v>14335.17</v>
-      </c>
-      <c r="E37" s="6" t="n">
+      <c r="D51" s="6" t="n">
+        <v>14082.15</v>
+      </c>
+      <c r="E51" s="6" t="n">
         <v>19892.4</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F51" s="6" t="n">
         <v>14079.83</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G51" s="6" t="n">
         <v>2000</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>124.64</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>124.64</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>INTROMEX S.A.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2606,137 +2606,317 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>1 de 35</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>2 de 35</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
-        </is>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>0 de 35</t>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>2 de 38</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
         </is>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>2368.22</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>2 de 38</t>
+          <t>3 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>2368.22</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>19892.4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>14079.83</v>
+        <v>16448.05</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6368.04</v>
+        <v>6343.79</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>7743.69</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7674.41</v>
+        <v>7650.16</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>19892.4</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>16448.05</v>
+        <v>16423.8</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>REYES GUILLEN VICTOR EUGENIO</t>
+          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
+          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
+          <t>TORRES KUON YENG LETICIA AMERICA</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -4277,46 +4277,19 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>TORRES KUON YENG LETICIA AMERICA</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="6" t="n">
+      <c r="C50" s="6" t="n">
         <v>31011.48</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D50" s="6" t="n">
         <v>14082.15</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E50" s="6" t="n">
         <v>19892.4</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F50" s="6" t="n">
         <v>16423.8</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G50" s="6" t="n">
         <v>2000</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>302.4</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>7694.7</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2841,57 +2841,57 @@
     <row r="40">
       <c r="C40" s="4" t="inlineStr">
         <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>1 de 38</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>1 de 38</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>3 de 38</t>
+          <t>4 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3595,7 +3595,7 @@
         <v>10297.46</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>7997.1</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>16423.8</v>
+        <v>24420.9</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7694.7</v>
+        <v>7603.71</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>10297.46</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7997.1</v>
+        <v>7906.11</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>24420.9</v>
+        <v>24329.91</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7603.71</v>
+        <v>7625.31</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>10297.46</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7906.11</v>
+        <v>7927.71</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>24329.91</v>
+        <v>24351.51</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4304,7 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4359,16 +4359,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>302.4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>-180.4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>2.478688524590164</v>
       </c>
     </row>
     <row r="3">
@@ -4383,16 +4383,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1514</v>
+        <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3812.32</v>
+        <v>1306.37</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2298.32</v>
+        <v>1143.63</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.518044914134742</v>
+        <v>0.5332122448979592</v>
       </c>
     </row>
     <row r="4">
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>959.02</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-759.52</v>
+        <v>198</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4.807117794486215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4431,13 +4431,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>133.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -4455,16 +4455,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>347.55</v>
+        <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-59.4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>406.95</v>
+        <v>312</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.1709106603366422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4527,16 +4527,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>124.64</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>203.763</v>
+        <v>275.36</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.3116</v>
       </c>
     </row>
     <row r="10">
@@ -4551,16 +4551,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>460</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-84.25</v>
+        <v>21.06</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>544.25</v>
+        <v>198.94</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.1831521739130435</v>
+        <v>0.09572727272727272</v>
       </c>
     </row>
     <row r="11">
@@ -4575,16 +4575,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2105</v>
+        <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>685.84</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1419.16</v>
+        <v>574</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.3258147268408551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4599,16 +4599,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>25250</v>
+        <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14578.87</v>
+        <v>22597.04</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10671.13</v>
+        <v>21501.96</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5773809900990099</v>
+        <v>0.5124161545613279</v>
       </c>
     </row>
     <row r="13">
@@ -4623,59 +4623,35 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>327.6</v>
+        <v>228</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>327.6</v>
+        <v>228</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAL SOLUBLE</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>24351.51</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>24634.99</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>30830.233</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>19892.4</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>10937.833</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.6452237970436357</v>
+        <v>0.4971065497637104</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>13558.54</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>4 de 38</t>
+          <t>5 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3190,7 +3190,7 @@
         <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>13558.54</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>24351.51</v>
+        <v>37910.05</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4311,7 +4311,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22597.04</v>
+        <v>36155.58</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>21501.96</v>
+        <v>7943.419999999998</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5124161545613279</v>
+        <v>0.8198730129934919</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>24351.51</v>
+        <v>37910.05</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>24634.99</v>
+        <v>11076.45</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.4971065497637104</v>
+        <v>0.7738877037551163</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13558.54</v>
+        <v>13493.58</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13558.54</v>
+        <v>13493.58</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>37910.05</v>
+        <v>37845.09</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>36155.58</v>
+        <v>36090.62</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7943.419999999998</v>
+        <v>8008.379999999997</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8198730129934919</v>
+        <v>0.8183999637179982</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>37910.05</v>
+        <v>37845.09</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11076.45</v>
+        <v>11141.41</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7738877037551163</v>
+        <v>0.7725616241209313</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13493.58</v>
+        <v>30259.92</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>124.64</v>
+        <v>264.88</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13493.58</v>
+        <v>30259.92</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3676,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>145.7</v>
+        <v>347.83</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>37845.09</v>
+        <v>54813.56</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4311,8 +4311,8 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4530,13 +4530,13 @@
         <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>124.64</v>
+        <v>264.88</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>275.36</v>
+        <v>135.12</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.3116</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="10">
@@ -4554,13 +4554,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>21.06</v>
+        <v>82.95</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>198.94</v>
+        <v>137.05</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.09572727272727272</v>
+        <v>0.3770454545454546</v>
       </c>
     </row>
     <row r="11">
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>36090.62</v>
+        <v>52856.96</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8008.379999999997</v>
+        <v>-8757.959999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8183999637179982</v>
+        <v>1.198597700628132</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>37845.09</v>
+        <v>54813.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11141.41</v>
+        <v>-5827.059999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7725616241209313</v>
+        <v>1.118952364426934</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30259.92</v>
+        <v>30286.92</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6259.72</v>
+        <v>6286.72</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>30259.92</v>
+        <v>30286.92</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6259.72</v>
+        <v>6286.72</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>54813.56</v>
+        <v>54867.56</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>52856.96</v>
+        <v>52910.96</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8757.959999999999</v>
+        <v>-8811.959999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.198597700628132</v>
+        <v>1.199822218190889</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>54813.56</v>
+        <v>54867.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-5827.059999999999</v>
+        <v>-5881.059999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.118952364426934</v>
+        <v>1.120054708950425</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,10 +597,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>342.92</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>83.69</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
+        <v>440.03</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -2866,19 +2866,19 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>1 de 38</t>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>1 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>5 de 38</t>
+          <t>7 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3028,7 +3028,7 @@
         <v>976.48</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>426.61</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>2000</v>
@@ -3082,7 +3082,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2368.22</v>
+        <v>2808.25</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>54867.56</v>
+        <v>56709.77</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4311,7 +4311,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>440.03</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-440.03</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>82.95</v>
+        <v>1031.52</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>137.05</v>
+        <v>-811.52</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.3770454545454546</v>
+        <v>4.688727272727273</v>
       </c>
     </row>
     <row r="11">
@@ -4578,13 +4578,13 @@
         <v>574</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>342.92</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>574</v>
+        <v>231.08</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.5974216027874565</v>
       </c>
     </row>
     <row r="12">
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>52910.96</v>
+        <v>53021.65</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8811.959999999999</v>
+        <v>-8922.650000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.199822218190889</v>
+        <v>1.202332252432028</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>54867.56</v>
+        <v>56709.77</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-5881.059999999999</v>
+        <v>-7723.270000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.120054708950425</v>
+        <v>1.157661192369326</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30286.92</v>
+        <v>30185.39</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>874.77</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>30286.92</v>
+        <v>30185.39</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>56709.77</v>
+        <v>56608.24</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4602,13 +4602,13 @@
         <v>44099</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>53021.65</v>
+        <v>52920.12</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8922.650000000001</v>
+        <v>-8821.120000000003</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.202332252432028</v>
+        <v>1.200029932651534</v>
       </c>
     </row>
     <row r="13">
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56709.77</v>
+        <v>56608.24000000001</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-7723.270000000001</v>
+        <v>-7621.740000000003</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.157661192369326</v>
+        <v>1.155588580527288</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>440.03</v>
+        <v>132.01</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2808.25</v>
+        <v>2500.23</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>19892.4</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>56608.24</v>
+        <v>56300.22</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>440.03</v>
+        <v>132.01</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-440.03</v>
+        <v>-132.01</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>48986.5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>56608.24000000001</v>
+        <v>56300.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-7621.740000000003</v>
+        <v>-7313.720000000003</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.155588580527288</v>
+        <v>1.149300725710145</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,10 +597,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>342.92</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>83.69</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>132.01</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2368.22</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>30185.39</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1306.37</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6343.79</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6286.72</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>302.4</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7625.31</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>264.88</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -2841,12 +2841,12 @@
     <row r="40">
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>7 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2936,10 +2936,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2956,22 +2956,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3019,16 +3019,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>2643.95</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2643.95</v>
+        <v>976.48</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>976.48</v>
+        <v>426.61</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>426.61</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>2000</v>
@@ -3073,16 +3073,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4071.3</v>
+        <v>1375.8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3127,16 +3127,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5486.41</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>2500.23</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2500.23</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>2375.07</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2375.07</v>
+        <v>874.77</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>874.77</v>
+        <v>30185.39</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>30185.39</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3235,16 +3235,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17271.64</v>
+        <v>3400.15</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3400.15</v>
+        <v>7743.69</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7743.69</v>
+        <v>7650.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7650.16</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -3343,16 +3343,16 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>3033.21</v>
+        <v>4406.39</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4406.39</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>6286.72</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>6286.72</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>-253.02</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>-253.02</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>27</v>
+        <v>133.81</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>133.81</v>
+        <v>10297.46</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10297.46</v>
+        <v>8071.53</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7927.71</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>282.62</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>347.83</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>347.83</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -3991,16 +3991,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>839.3</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0</v>
@@ -4278,16 +4278,16 @@
     </row>
     <row r="50">
       <c r="C50" s="6" t="n">
-        <v>31011.48</v>
+        <v>14082.15</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>14082.15</v>
+        <v>19892.4</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>19892.4</v>
+        <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>56300.22</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>2000</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4290,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>1166.13</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0</v>
+        <v>685.8</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1211.76</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0</v>
+        <v>1828.8</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>0</v>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>2 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>2 de 38</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3028,7 +3028,7 @@
         <v>426.61</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1166.13</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>27</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>685.8</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>30185.39</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>1211.76</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>1828.8</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>4892.49</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4304,15 +4304,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4359,16 +4359,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>122</v>
+        <v>500</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>302.4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-180.4</v>
+        <v>500</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.478688524590164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4386,13 +4386,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1306.37</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1143.63</v>
+        <v>2450</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5332122448979592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4506,10 +4506,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>132.01</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-132.01</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4530,13 +4530,13 @@
         <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>264.88</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135.12</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.6622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4554,13 +4554,13 @@
         <v>220</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1031.52</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-811.52</v>
+        <v>220</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4.688727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4571,20 +4571,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>574</v>
+        <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>342.92</v>
+        <v>2377.89</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>231.08</v>
+        <v>36822.11</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.5974216027874565</v>
+        <v>0.06066045918367347</v>
       </c>
     </row>
     <row r="12">
@@ -4595,63 +4595,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>44099</v>
+        <v>570</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>52920.12</v>
+        <v>2514.6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-8821.120000000003</v>
+        <v>-1944.6</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.200029932651534</v>
+        <v>4.411578947368421</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>228</v>
+        <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>4892.49</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>228</v>
+        <v>39341.01</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>48986.5</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>56300.22</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-7313.720000000003</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.149300725710145</v>
+        <v>0.1106059886737427</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1828.8</v>
+        <v>1371.6</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1828.8</v>
+        <v>1371.6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>4892.49</v>
+        <v>4435.29</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -4602,13 +4602,13 @@
         <v>570</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2514.6</v>
+        <v>2057.4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-1944.6</v>
+        <v>-1487.4</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4.411578947368421</v>
+        <v>3.609473684210526</v>
       </c>
     </row>
     <row r="13">
@@ -4621,13 +4621,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4892.49</v>
+        <v>4435.29</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39341.01</v>
+        <v>39798.21</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1106059886737427</v>
+        <v>0.1002699311607718</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>130.61</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>1 de 38</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>347.83</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>130.61</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>4435.29</v>
+        <v>4565.9</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0</v>
@@ -4311,7 +4311,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4410,13 +4410,13 @@
         <v>198</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>130.61</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>198</v>
+        <v>67.38999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.6596464646464647</v>
       </c>
     </row>
     <row r="5">
@@ -4621,13 +4621,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4435.29</v>
+        <v>4565.9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39798.21</v>
+        <v>39667.6</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1002699311607718</v>
+        <v>0.1032226706003368</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3031,7 +3031,7 @@
         <v>1166.13</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -3085,7 +3085,7 @@
         <v>685.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
@@ -3193,7 +3193,7 @@
         <v>1211.76</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="10">
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="12">
@@ -3328,7 +3328,7 @@
         <v>1371.6</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="16">
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19">
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="25">
@@ -3679,7 +3679,7 @@
         <v>130.61</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="28">
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="44">
@@ -4290,7 +4290,7 @@
         <v>4565.9</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>43500</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>442.32</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>2419.82</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>1011.58</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>23.06</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2846,52 +2846,52 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>1 de 38</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>2 de 38</t>
+          <t>4 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3190,7 +3190,7 @@
         <v>30185.39</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1211.76</v>
+        <v>1654.08</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>12000</v>
@@ -3595,7 +3595,7 @@
         <v>8071.53</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>2419.82</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>7000</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0</v>
+        <v>1034.64</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1500</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>4565.9</v>
+        <v>8462.68</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>43500</v>
@@ -4312,7 +4312,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4386,13 +4386,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>1011.58</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2450</v>
+        <v>1438.42</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.4128897959183674</v>
       </c>
     </row>
     <row r="4">
@@ -4458,13 +4458,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>442.32</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>312</v>
+        <v>-130.32</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>1.417692307692308</v>
       </c>
     </row>
     <row r="7">
@@ -4578,13 +4578,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2377.89</v>
+        <v>4820.77</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>36822.11</v>
+        <v>34379.23</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.06066045918367347</v>
+        <v>0.1229788265306123</v>
       </c>
     </row>
     <row r="12">
@@ -4621,13 +4621,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>4565.9</v>
+        <v>8462.68</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>39667.6</v>
+        <v>35770.82</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1032226706003368</v>
+        <v>0.1913183446935015</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>2660.89</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2729.08</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2846,52 +2846,52 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
+          <t>2 de 38</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
           <t>1 de 38</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>1 de 38</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>1 de 38</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>4 de 38</t>
+          <t>5 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3244,7 +3244,7 @@
         <v>7650.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>5389.97</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>5500</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>8462.68</v>
+        <v>13852.65</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>43500</v>
@@ -4386,13 +4386,13 @@
         <v>2450</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1011.58</v>
+        <v>3672.47</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1438.42</v>
+        <v>-1222.47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4128897959183674</v>
+        <v>1.498967346938775</v>
       </c>
     </row>
     <row r="4">
@@ -4578,13 +4578,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4820.77</v>
+        <v>7549.85</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>34379.23</v>
+        <v>31650.15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1229788265306123</v>
+        <v>0.1925982142857143</v>
       </c>
     </row>
     <row r="12">
@@ -4621,13 +4621,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8462.68</v>
+        <v>13852.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>35770.82</v>
+        <v>30380.85</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1913183446935015</v>
+        <v>0.3131710129200719</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3031,7 +3031,7 @@
         <v>1166.13</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2000</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="4">
@@ -3085,7 +3085,7 @@
         <v>685.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2500</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3193,7 +3193,7 @@
         <v>1654.08</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12000</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="10">
@@ -3247,7 +3247,7 @@
         <v>5389.97</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5500</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="12">
@@ -3328,7 +3328,7 @@
         <v>1371.6</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1500</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="15">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3598,7 +3598,7 @@
         <v>2419.82</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7000</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="25">
@@ -3679,7 +3679,7 @@
         <v>130.61</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2500</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28">
@@ -3706,7 +3706,7 @@
         <v>1034.64</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1500</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="29">
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4290,7 +4290,7 @@
         <v>13852.65</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>43500</v>
+        <v>13854</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2729.08</v>
+        <v>2688.14</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>7650.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5389.97</v>
+        <v>5349.03</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>5390</v>
@@ -4287,7 +4287,7 @@
         <v>56444.04</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>13852.65</v>
+        <v>13811.71</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>13854</v>
@@ -4578,13 +4578,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7549.85</v>
+        <v>7508.91</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31650.15</v>
+        <v>31691.09</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1925982142857143</v>
+        <v>0.1915538265306122</v>
       </c>
     </row>
     <row r="12">
@@ -4621,13 +4621,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13852.65</v>
+        <v>13811.71</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>30380.85</v>
+        <v>30421.79</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3131710129200719</v>
+        <v>0.3122454700622831</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2931,11 +2931,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -3366,11 +3366,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA &amp; CONSTRUCTORA ELECTRICA PALAU &amp; ORTIZ MEGA-ENERGYCORP SA</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>-253.02</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -3393,11 +3393,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-253.02</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COZZARELLI CONTRERAS FATIMA MERCEDES</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -3528,23 +3528,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>133.81</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>10297.46</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>8071.53</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>2419.82</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="23">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>FULLCONSTRU S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3582,23 +3582,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>133.81</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>10297.46</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>8071.53</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2419.82</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FULLCONSTRU S.A.</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3619,13 +3619,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>347.83</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>130.61</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3649,10 +3649,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>1034.64</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="27">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3673,13 +3673,13 @@
         <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>347.83</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>130.61</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3703,10 +3703,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1034.64</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>INTROMEX S.A.</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>INTROMEX S.A.</t>
+          <t>LIBERIO SUAREZ PEDRO ADAN</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LIBERIO SUAREZ PEDRO ADAN</t>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+          <t>MEJIA FERRIN HOLGER EDEN</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MEJIA FERRIN HOLGER EDEN</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>MUÑOZ FALCONEZ SIGIFREDO DOMINGO</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>PROAÑO CELA BLANCA LUCILA</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONEZ SIGIFREDO DOMINGO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PROAÑO CELA BLANCA LUCILA</t>
+          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>TORRES KUON YENG LETICIA AMERICA</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -4223,73 +4223,19 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>TORRES KUON YENG LETICIA AMERICA</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="6" t="n">
+      <c r="C48" s="6" t="n">
         <v>14082.15</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D48" s="6" t="n">
         <v>19892.4</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E48" s="6" t="n">
         <v>56444.04</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F48" s="6" t="n">
         <v>13811.71</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G48" s="6" t="n">
         <v>13854</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2839,84 +2839,144 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>2 de 38</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>1 de 38</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>1 de 38</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>5 de 38</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>2 de 38</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="R40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>2 de 39</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>5 de 39</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>2 de 39</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4203,39 +4263,66 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>TORRES KUON YENG LETICIA AMERICA</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="6" t="n">
         <v>14082.15</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D49" s="6" t="n">
         <v>19892.4</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E49" s="6" t="n">
         <v>56444.04</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F49" s="6" t="n">
         <v>13811.71</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G49" s="6" t="n">
         <v>13854</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2991,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3048,23 +3048,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AJILA CRUZ JOSE CHI</t>
+          <t>ALARCON MAYORGA LUIS ALFONSO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>2643.95</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>976.48</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>426.61</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1166.13</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="3">
@@ -3075,23 +3075,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALARCON MAYORGA LUIS ALFONSO</t>
+          <t>ANGAMARCA CURIPONA WILMA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2643.95</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>976.48</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>426.61</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1166.13</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3102,23 +3102,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>1375.8</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>685.8</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5">
@@ -3129,23 +3129,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>685.8</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2500.23</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BARRETO CHAVARRIA RENZO DUVAL</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2500.23</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -3210,23 +3210,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BARRETO CHAVARRIA RENZO DUVAL</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>2375.07</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>874.77</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>30185.39</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>1654.08</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="9">
@@ -3237,23 +3237,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2375.07</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>874.77</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>30185.39</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1654.08</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3264,23 +3264,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0</v>
+        <v>3400.15</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>7743.69</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>7650.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>5349.03</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="11">
@@ -3291,23 +3291,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CALERO LOPEZ GISELLA JACKELINE</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3400.15</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7743.69</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7650.16</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5349.03</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>1371.6</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="14">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>4406.39</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>6286.72</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3399,17 +3399,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4406.39</v>
+        <v>-253.02</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6286.72</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -3426,11 +3426,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-253.02</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -3561,23 +3561,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>133.81</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>10297.46</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>8071.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>2419.82</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="22">
@@ -3588,23 +3588,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>133.81</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10297.46</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8071.53</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2419.82</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FULLCONSTRU S.A.</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>347.83</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>130.61</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3655,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>1034.64</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>347.83</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>130.61</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1034.64</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>INTROMEX S.A.</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INTROMEX S.A.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LIBERIO SUAREZ PEDRO ADAN</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MEJIA FERRIN HOLGER EDEN</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONEZ SIGIFREDO DOMINGO</t>
+          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -4040,289 +4040,19 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>PROAÑO CELA BLANCA LUCILA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ROSERO ALDAZ JUAN AGUSTIN</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>TORRES KUON YENG LETICIA AMERICA</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="6" t="n">
+      <c r="C39" s="6" t="n">
         <v>14082.15</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D39" s="6" t="n">
         <v>19892.4</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E39" s="6" t="n">
         <v>56444.04</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>13811.71</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G39" s="6" t="n">
         <v>13854</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2419.82</v>
+        <v>2395.38</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>8071.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2419.82</v>
+        <v>2395.38</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -4050,7 +4050,7 @@
         <v>56444.04</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>13811.71</v>
+        <v>13787.27</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4341,13 +4341,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7508.91</v>
+        <v>7484.47</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31691.09</v>
+        <v>31715.53</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1915538265306122</v>
+        <v>0.1909303571428571</v>
       </c>
     </row>
     <row r="12">
@@ -4384,13 +4384,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13811.71</v>
+        <v>13787.27</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>30421.79</v>
+        <v>30446.23</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.3122454700622831</v>
+        <v>0.311692947652797</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>648.61</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>5105.52</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>2 de 39</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>5 de 39</t>
+          <t>6 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
         <v>6286.72</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>5754.13</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>56444.04</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>13787.27</v>
+        <v>19541.4</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4073,8 +4073,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4221,13 +4221,13 @@
         <v>312</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>442.32</v>
+        <v>1090.93</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-130.32</v>
+        <v>-778.9300000000001</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.417692307692308</v>
+        <v>3.496570512820513</v>
       </c>
     </row>
     <row r="7">
@@ -4341,13 +4341,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7484.47</v>
+        <v>12589.99</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31715.53</v>
+        <v>26610.01</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1909303571428571</v>
+        <v>0.3211732142857143</v>
       </c>
     </row>
     <row r="12">
@@ -4384,13 +4384,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13787.27</v>
+        <v>19541.4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>30446.23</v>
+        <v>24692.1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.311692947652797</v>
+        <v>0.4417782902099088</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>3091.56</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>685.8</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2688.14</v>
+        <v>4749.18</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2395.38</v>
+        <v>8594.790000000001</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>23.06</v>
+        <v>6823.62</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2941,17 +2941,17 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>6 de 39</t>
+          <t>7 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3115,7 +3115,7 @@
         <v>27</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>685.8</v>
+        <v>3777.36</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>686</v>
@@ -3277,7 +3277,7 @@
         <v>7650.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5349.03</v>
+        <v>7410.07</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3574,7 +3574,7 @@
         <v>8071.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2395.38</v>
+        <v>8607.540000000001</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1034.64</v>
+        <v>7835.2</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1035</v>
@@ -4050,7 +4050,7 @@
         <v>56444.04</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>19541.4</v>
+        <v>37706.72</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4293,13 +4293,13 @@
         <v>400</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>400</v>
+        <v>387.25</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.031875</v>
       </c>
     </row>
     <row r="10">
@@ -4341,13 +4341,13 @@
         <v>39200</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12589.99</v>
+        <v>30742.56</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>26610.01</v>
+        <v>8457.439999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.3211732142857143</v>
+        <v>0.7842489795918368</v>
       </c>
     </row>
     <row r="12">
@@ -4384,13 +4384,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>19541.4</v>
+        <v>37706.72</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24692.1</v>
+        <v>6526.779999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4417782902099088</v>
+        <v>0.8524471271773656</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>74.36</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>130.61</v>
+        <v>204.88</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>2 de 39</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3574,7 +3574,7 @@
         <v>8071.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>8607.540000000001</v>
+        <v>8681.9</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -3628,7 +3628,7 @@
         <v>347.83</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>130.61</v>
+        <v>204.88</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>131</v>
@@ -4050,7 +4050,7 @@
         <v>56444.04</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>37706.72</v>
+        <v>37855.35</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4173,13 +4173,13 @@
         <v>198</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>130.61</v>
+        <v>279.24</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>67.38999999999999</v>
+        <v>-81.24000000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.6596464646464647</v>
+        <v>1.41030303030303</v>
       </c>
     </row>
     <row r="5">
@@ -4384,13 +4384,13 @@
         <v>44233.5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>37706.72</v>
+        <v>37855.35000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6526.779999999999</v>
+        <v>6378.149999999998</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.8524471271773656</v>
+        <v>0.8558072501610772</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1166.13</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
@@ -720,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3091.56</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>685.8</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>442.32</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1211.76</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2660.89</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4749.18</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>648.61</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0</v>
@@ -1260,7 +1260,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5105.52</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>74.36</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8594.790000000001</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>204.88</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1011.58</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6823.62</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>7 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -2996,10 +2996,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3016,22 +3016,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3052,16 +3052,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2643.95</v>
+        <v>976.48</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>976.48</v>
+        <v>426.61</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>426.61</v>
+        <v>1166.13</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1166.13</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1166</v>
@@ -3106,16 +3106,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1375.8</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27</v>
+        <v>3777.36</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3777.36</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>686</v>
@@ -3163,10 +3163,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2500.23</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2500.23</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2375.07</v>
+        <v>874.77</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>874.77</v>
+        <v>30185.39</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30185.39</v>
+        <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1654.08</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3400.15</v>
+        <v>7743.69</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7743.69</v>
+        <v>7650.16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7650.16</v>
+        <v>7410.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>7410.07</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3355,10 +3355,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>1371.6</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1372</v>
@@ -3376,16 +3376,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4406.39</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>6286.72</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6286.72</v>
+        <v>5754.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5754.13</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-253.02</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
@@ -3565,16 +3565,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>133.81</v>
+        <v>10297.46</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10297.46</v>
+        <v>8071.53</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8071.53</v>
+        <v>8681.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>8681.9</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -3622,13 +3622,13 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>347.83</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>347.83</v>
+        <v>204.88</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>204.88</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>131</v>
@@ -3652,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>7835.2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7835.2</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1035</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
@@ -4041,16 +4041,16 @@
     </row>
     <row r="39">
       <c r="C39" s="6" t="n">
-        <v>14082.15</v>
+        <v>19892.4</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>19892.4</v>
+        <v>56444.04</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>56444.04</v>
+        <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>37855.35</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -455,7 +455,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3223,7 +3223,7 @@
         <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>-15.61</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>7410.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>-15.61</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>104.56</v>
+        <v>88.95</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1674.18</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3223,7 +3223,7 @@
         <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>104.56</v>
+        <v>1778.74</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>88.95</v>
+        <v>1763.13</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>832.61</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1674.18</v>
+        <v>5783.14</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>243.65</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2911,29 +2911,29 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -3223,7 +3223,7 @@
         <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1778.74</v>
+        <v>6720.31</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>243.65</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1763.13</v>
+        <v>6948.35</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4067,14 +4067,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4122,13 +4122,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>500</v>
+        <v>136.08</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -4146,16 +4146,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2450</v>
+        <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3672.47</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1222.47</v>
+        <v>1514</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.498967346938775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4170,16 +4170,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>198</v>
+        <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>279.24</v>
+        <v>832.61</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-81.24000000000001</v>
+        <v>-633.11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.41030303030303</v>
+        <v>4.173483709273183</v>
       </c>
     </row>
     <row r="5">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>133.5</v>
+        <v>172.82</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>133.5</v>
+        <v>172.82</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -4218,16 +4218,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1090.93</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-778.9300000000001</v>
+        <v>263</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>3.496570512820513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4269,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>-104.56</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>400</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>12.75</v>
+        <v>243.65</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>387.25</v>
+        <v>-39.887</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.031875</v>
+        <v>1.195751927484381</v>
       </c>
     </row>
     <row r="10">
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -4334,20 +4334,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>39200</v>
+        <v>1600</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>30742.56</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8457.439999999999</v>
+        <v>1600</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7842489795918368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4358,39 +4358,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>29057</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5767.53</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>23289.47</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.1984902088997487</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>570</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>2057.4</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-1487.4</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>3.609473684210526</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>44233.5</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>37855.35000000001</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>6378.149999999998</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.8558072501610772</v>
+      <c r="C14" s="2" t="n">
+        <v>34944.963</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6948.35</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>27996.613</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.1988369539838975</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>15.24</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>2 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
         <v>204.88</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>15.24</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>131</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>6948.35</v>
+        <v>6963.59</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5767.53</v>
+        <v>5782.77</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23289.47</v>
+        <v>23274.23</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1984902088997487</v>
+        <v>0.1990146952541556</v>
       </c>
     </row>
     <row r="13">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6948.35</v>
+        <v>6963.59</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27996.613</v>
+        <v>27981.373</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1988369539838975</v>
+        <v>0.1992730683389191</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>610.15</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>104.56</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>2493.92</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         <v>243.65</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1083.62</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>3 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3223,7 +3223,7 @@
         <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6720.31</v>
+        <v>7330.46</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>2493.92</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>243.65</v>
+        <v>1327.27</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>6963.59</v>
+        <v>11151.28</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4074,7 +4074,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4221,13 +4221,13 @@
         <v>263</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>610.15</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>263</v>
+        <v>-347.15</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2.319961977186312</v>
       </c>
     </row>
     <row r="7">
@@ -4341,13 +4341,13 @@
         <v>1600</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1083.62</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1600</v>
+        <v>516.3800000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.6772624999999999</v>
       </c>
     </row>
     <row r="12">
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5782.77</v>
+        <v>8276.690000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23274.23</v>
+        <v>20780.31</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1990146952541556</v>
+        <v>0.284843239150635</v>
       </c>
     </row>
     <row r="13">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6963.59</v>
+        <v>11151.28</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27981.373</v>
+        <v>23793.683</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1992730683389191</v>
+        <v>0.3191097955948615</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>211.24</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>6501.7</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
@@ -2906,47 +2906,47 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>1 de 39</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
           <t>0 de 39</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>1 de 39</t>
-        </is>
-      </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>2 de 39</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
         <v>5754.13</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>6712.94</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>11151.28</v>
+        <v>17864.22</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4074,7 +4074,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4149,13 +4149,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>211.24</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1514</v>
+        <v>1302.76</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>0.1395244385733157</v>
       </c>
     </row>
     <row r="4">
@@ -4341,13 +4341,13 @@
         <v>1600</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1083.62</v>
+        <v>7585.32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>516.3800000000001</v>
+        <v>-5985.32</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.6772624999999999</v>
+        <v>4.740825</v>
       </c>
     </row>
     <row r="12">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11151.28</v>
+        <v>17864.22</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>23793.683</v>
+        <v>17080.743</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3191097955948615</v>
+        <v>0.5112101563821945</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-15.61</v>
+        <v>5068.59</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>3 de 39</t>
+          <t>4 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3277,7 +3277,7 @@
         <v>7410.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-15.61</v>
+        <v>5068.59</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>17864.22</v>
+        <v>22948.42</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4073,7 +4073,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8276.690000000001</v>
+        <v>13360.89</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20780.31</v>
+        <v>15696.11</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.284843239150635</v>
+        <v>0.4598165674364181</v>
       </c>
     </row>
     <row r="13">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>17864.22</v>
+        <v>22948.42</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17080.743</v>
+        <v>11996.543</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.5112101563821945</v>
+        <v>0.6567017970515521</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5068.59</v>
+        <v>8226.940000000001</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>7410.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5068.59</v>
+        <v>8226.940000000001</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>22948.42</v>
+        <v>26106.77</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13360.89</v>
+        <v>16519.24</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15696.11</v>
+        <v>12537.76</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.4598165674364181</v>
+        <v>0.5685115462711223</v>
       </c>
     </row>
     <row r="13">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>22948.42</v>
+        <v>26106.77</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11996.543</v>
+        <v>8838.192999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6567017970515521</v>
+        <v>0.7470824908299373</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5783.14</v>
+        <v>12240.35</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8226.940000000001</v>
+        <v>8184.38</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2999,7 +2999,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3223,7 +3223,7 @@
         <v>1654.08</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7330.46</v>
+        <v>13787.67</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3277,7 +3277,7 @@
         <v>7410.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8226.940000000001</v>
+        <v>8184.38</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>26106.77</v>
+        <v>32521.42</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4074,7 +4074,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>16519.24</v>
+        <v>22933.89</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12537.76</v>
+        <v>6123.110000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.5685115462711223</v>
+        <v>0.7892724644663937</v>
       </c>
     </row>
     <row r="13">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>26106.77</v>
+        <v>32521.42</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8838.192999999999</v>
+        <v>2423.543000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7470824908299373</v>
+        <v>0.9306468574598289</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>1299.17</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -840,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>1141.84</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0</v>
+        <v>457.2</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>5421.72</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -2906,57 +2906,57 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
+          <t>3 de 39</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>0 de 39</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>2 de 39</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>2 de 39</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>5 de 39</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>1 de 39</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>1 de 39</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>2 de 39</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>4 de 39</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>2898.21</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>8681.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>5421.72</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -3628,7 +3628,7 @@
         <v>204.88</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>15.24</v>
+        <v>109.48</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>131</v>
@@ -4050,7 +4050,7 @@
         <v>37855.35</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>32521.42</v>
+        <v>40935.59</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4149,13 +4149,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>211.24</v>
+        <v>6932.13</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1302.76</v>
+        <v>-5418.13</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1395244385733157</v>
+        <v>4.578685601056804</v>
       </c>
     </row>
     <row r="4">
@@ -4293,13 +4293,13 @@
         <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>243.65</v>
+        <v>337.89</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-39.887</v>
+        <v>-134.127</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.195751927484381</v>
+        <v>1.658250025765227</v>
       </c>
     </row>
     <row r="10">
@@ -4365,13 +4365,13 @@
         <v>29057</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22933.89</v>
+        <v>24075.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6123.110000000001</v>
+        <v>4981.27</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7892724644663937</v>
+        <v>0.8285690195133703</v>
       </c>
     </row>
     <row r="13">
@@ -4389,13 +4389,13 @@
         <v>1198.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>457.2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1198.8</v>
+        <v>741.5999999999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.3813813813813814</v>
       </c>
     </row>
     <row r="14">
@@ -4408,13 +4408,13 @@
         <v>34944.963</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>32521.42</v>
+        <v>40935.59</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2423.543000000001</v>
+        <v>-5990.626999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9306468574598289</v>
+        <v>1.171430343194239</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -455,7 +455,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1299.17</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -840,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1141.84</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>457.2</v>
+        <v>0</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>832.61</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -888,10 +888,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>610.15</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>104.56</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12240.35</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8184.38</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>211.24</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6501.7</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5421.72</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1914,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>94.23999999999999</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15.24</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2493.92</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>243.65</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1083.62</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0</v>
@@ -2906,12 +2906,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>3 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>5 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>1 de 39</t>
+          <t>0 de 39</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
@@ -2997,9 +2997,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3016,22 +3016,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -3052,13 +3052,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>976.48</v>
+        <v>426.61</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>426.61</v>
+        <v>1166.13</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1166.13</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -3106,13 +3106,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>27</v>
+        <v>3777.36</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3777.36</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -3160,16 +3160,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>2500.23</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2500.23</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>2898.21</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2898.21</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -3214,16 +3214,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>874.77</v>
+        <v>30185.39</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>30185.39</v>
+        <v>1654.08</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1654.08</v>
+        <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13787.67</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7743.69</v>
+        <v>7650.16</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7650.16</v>
+        <v>7410.07</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7410.07</v>
+        <v>8184.38</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8184.38</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3352,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>1371.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -3376,16 +3376,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>6286.72</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6286.72</v>
+        <v>5754.13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5754.13</v>
+        <v>6712.94</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6712.94</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -3565,16 +3565,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10297.46</v>
+        <v>8071.53</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8071.53</v>
+        <v>8681.9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8681.9</v>
+        <v>5421.72</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>5421.72</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>2420</v>
@@ -3619,16 +3619,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>347.83</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>347.83</v>
+        <v>204.88</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>204.88</v>
+        <v>109.48</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>109.48</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>131</v>
@@ -3649,10 +3649,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>7835.2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>7835.2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0</v>
@@ -3706,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>2493.92</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2493.92</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -3835,16 +3835,16 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0</v>
+        <v>948.5700000000001</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0</v>
+        <v>1327.27</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1327.27</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -4041,16 +4041,16 @@
     </row>
     <row r="39">
       <c r="C39" s="6" t="n">
-        <v>19892.4</v>
+        <v>56444.04</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>56444.04</v>
+        <v>37855.35</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>37855.35</v>
+        <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>40935.59</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>8313.379999999999</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>0 de 39</t>
+          <t>1 de 39</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3277,7 +3277,7 @@
         <v>8184.38</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>8313.379999999999</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -4050,7 +4050,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0</v>
+        <v>8313.379999999999</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>-78.06</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3223,7 +3223,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>-78.06</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -4050,7 +4050,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8313.379999999999</v>
+        <v>8235.32</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INTROMEX S.A.</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>MINUTOCORP S.A.</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
+          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -2839,144 +2839,84 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>1 de 39</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
-        </is>
-      </c>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>0 de 39</t>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>0 de 38</t>
         </is>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8313.379999999999</v>
+        <v>8236.48</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -3217,7 +3217,7 @@
         <v>8184.38</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8313.379999999999</v>
+        <v>8236.48</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8235.32</v>
+        <v>8158.419999999999</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>1 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1166</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8158.419999999999</v>
+        <v>8615.65</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4007,15 +4007,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4089,13 +4089,13 @@
         <v>1514</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6932.13</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5418.13</v>
+        <v>1514</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>4.578685601056804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4113,13 +4113,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>832.61</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-633.11</v>
+        <v>199.5</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4.173483709273183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4134,13 +4134,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172.82</v>
+        <v>198.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -4154,20 +4154,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>263</v>
+        <v>615</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>610.15</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-347.15</v>
+        <v>615</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2.319961977186312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4178,17 +4178,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>104.56</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-104.56</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4226,20 +4226,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>337.89</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-134.127</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.658250025765227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>350</v>
+        <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>350</v>
+        <v>203.763</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -4274,20 +4274,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1600</v>
+        <v>350</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7585.32</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-5985.32</v>
+        <v>350</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4.740825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4298,20 +4298,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>29057</v>
+        <v>4600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>24075.73</v>
+        <v>457.23</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4981.27</v>
+        <v>4142.77</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8285690195133703</v>
+        <v>0.09939782608695652</v>
       </c>
     </row>
     <row r="13">
@@ -4322,39 +4322,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>31648</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>8158.42</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>23489.58</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.2577862740141557</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C14" s="2" t="n">
         <v>1198.8</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>457.2</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>741.5999999999999</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.3813813813813814</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>34944.963</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>40935.59</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-5990.626999999999</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1.171430343194239</v>
+      <c r="C15" s="2" t="n">
+        <v>41376.643</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8615.65</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>32760.993</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.2082249640213683</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>2 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>8615.65</v>
+        <v>9123.559999999999</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4015,7 +4015,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4305,13 +4305,13 @@
         <v>4600</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>457.23</v>
+        <v>965.14</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4142.77</v>
+        <v>3634.86</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.09939782608695652</v>
+        <v>0.2098130434782609</v>
       </c>
     </row>
     <row r="13">
@@ -4372,13 +4372,13 @@
         <v>41376.643</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8615.65</v>
+        <v>9123.559999999999</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32760.993</v>
+        <v>32253.083</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2082249640213683</v>
+        <v>0.2205002469630027</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>3037.16</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>0 de 38</t>
+          <t>1 de 38</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3217,7 +3217,7 @@
         <v>8184.38</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8236.48</v>
+        <v>11273.64</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>9123.559999999999</v>
+        <v>12160.72</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4257,13 +4257,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>3037.16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>203.763</v>
+        <v>-2833.397</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>14.90535573190422</v>
       </c>
     </row>
     <row r="11">
@@ -4372,13 +4372,13 @@
         <v>41376.643</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9123.559999999999</v>
+        <v>12160.72</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>32253.083</v>
+        <v>29215.923</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2205002469630027</v>
+        <v>0.2939030118997328</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-78.06</v>
+        <v>-141.44</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-78.06</v>
+        <v>-141.44</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12160.72</v>
+        <v>12097.34</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4329,13 +4329,13 @@
         <v>31648</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8158.42</v>
+        <v>8095.04</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23489.58</v>
+        <v>23552.96</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2577862740141557</v>
+        <v>0.255783619817998</v>
       </c>
     </row>
     <row r="14">
@@ -4372,13 +4372,13 @@
         <v>41376.643</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12160.72</v>
+        <v>12097.34</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29215.923</v>
+        <v>29279.303</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2939030118997328</v>
+        <v>0.2923712298264506</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>81.22</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>2 de 38</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
         <v>1327.27</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0</v>
+        <v>81.22</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12097.34</v>
+        <v>12178.56</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4257,13 +4257,13 @@
         <v>203.763</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3037.16</v>
+        <v>3118.38</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-2833.397</v>
+        <v>-2914.617</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>14.90535573190422</v>
+        <v>15.30395606660679</v>
       </c>
     </row>
     <row r="11">
@@ -4372,13 +4372,13 @@
         <v>41376.643</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12097.34</v>
+        <v>12178.56</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>29279.303</v>
+        <v>29198.083</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.2923712298264506</v>
+        <v>0.2943341730260717</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -4007,7 +4007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4154,17 +4154,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INODOROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>615</v>
+        <v>463</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>615</v>
+        <v>463</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -4178,17 +4178,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>463</v>
+        <v>250</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>463</v>
+        <v>250</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4226,20 +4226,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>3118.38</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>-2914.617</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>15.30395606660679</v>
       </c>
     </row>
     <row r="10">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>203.763</v>
+        <v>350</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3118.38</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-2914.617</v>
+        <v>350</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>15.30395606660679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4274,20 +4274,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>PIEDRA SINTERIZADA</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>350</v>
+        <v>4600</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>965.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>350</v>
+        <v>3634.86</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>0.2098130434782609</v>
       </c>
     </row>
     <row r="12">
@@ -4298,20 +4298,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PORCELANATO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4600</v>
+        <v>31648</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>965.14</v>
+        <v>8095.04</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3634.86</v>
+        <v>23552.96</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.2098130434782609</v>
+        <v>0.255783619817998</v>
       </c>
     </row>
     <row r="13">
@@ -4322,63 +4322,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>31648</v>
+        <v>1198.8</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8095.04</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>23552.96</v>
+        <v>1198.8</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.255783619817998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PUERTAS DE SEGURIDAD</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1198.8</v>
+        <v>40761.643</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
+        <v>12178.56</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1198.8</v>
+        <v>28583.083</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>41376.643</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>12178.56</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>29198.083</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.2943341730260717</v>
+        <v>0.2987750027642408</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>394.76</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>108.29</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>81.22</v>
+        <v>270.66</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2851,37 +2851,37 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
+          <t>1 de 38</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>0 de 38</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>2 de 38</t>
+          <t>3 de 38</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -3163,7 +3163,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-141.44</v>
+        <v>361.61</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3784,7 +3784,7 @@
         <v>1327.27</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>81.22</v>
+        <v>270.66</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12178.56</v>
+        <v>12871.05</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4113,13 +4113,13 @@
         <v>199.5</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>394.76</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>199.5</v>
+        <v>-195.26</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1.97874686716792</v>
       </c>
     </row>
     <row r="5">
@@ -4233,13 +4233,13 @@
         <v>203.763</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3118.38</v>
+        <v>3416.11</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2914.617</v>
+        <v>-3212.347</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>15.30395606660679</v>
+        <v>16.76511437307068</v>
       </c>
     </row>
     <row r="10">
@@ -4348,13 +4348,13 @@
         <v>40761.643</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12178.56</v>
+        <v>12871.05</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28583.083</v>
+        <v>27890.593</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2987750027642408</v>
+        <v>0.3157637684035454</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-141.44</v>
+        <v>14378.05</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>2 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3163,7 +3163,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>361.61</v>
+        <v>14881.1</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>12871.05</v>
+        <v>27390.54</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4013,8 +4013,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4305,13 +4305,13 @@
         <v>31648</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8095.04</v>
+        <v>22614.53</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23552.96</v>
+        <v>9033.470000000001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.255783619817998</v>
+        <v>0.7145642694641051</v>
       </c>
     </row>
     <row r="13">
@@ -4348,13 +4348,13 @@
         <v>40761.643</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12871.05</v>
+        <v>27390.54</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>27890.593</v>
+        <v>13371.103</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.3157637684035454</v>
+        <v>0.6719684974425589</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>14378.05</v>
+        <v>16645.19</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -2697,10 +2697,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1998.71</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0</v>
+        <v>129.08</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2 de 38</t>
+          <t>3 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>2 de 38</t>
+          <t>3 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3163,7 +3163,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>14881.1</v>
+        <v>17148.24</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3919,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>2127.79</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>27390.54</v>
+        <v>31785.47</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4014,7 +4014,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4281,13 +4281,13 @@
         <v>4600</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>965.14</v>
+        <v>2963.85</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3634.86</v>
+        <v>1636.15</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2098130434782609</v>
+        <v>0.6443152173913044</v>
       </c>
     </row>
     <row r="12">
@@ -4305,13 +4305,13 @@
         <v>31648</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>22614.53</v>
+        <v>25010.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9033.470000000001</v>
+        <v>6637.25</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7145642694641051</v>
+        <v>0.7902790065722952</v>
       </c>
     </row>
     <row r="13">
@@ -4348,13 +4348,13 @@
         <v>40761.643</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>27390.54</v>
+        <v>31785.47</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13371.103</v>
+        <v>8976.172999999999</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6719684974425589</v>
+        <v>0.7797887342274206</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16645.19</v>
+        <v>22360.4</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>13787.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>17148.24</v>
+        <v>22863.45</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3990,7 +3990,7 @@
         <v>40935.59</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>31785.47</v>
+        <v>37500.68</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>
@@ -4014,7 +4014,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4305,13 +4305,13 @@
         <v>31648</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>25010.75</v>
+        <v>30725.96</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>6637.25</v>
+        <v>922.0400000000009</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.7902790065722952</v>
+        <v>0.9708657735085945</v>
       </c>
     </row>
     <row r="13">
@@ -4348,13 +4348,13 @@
         <v>40761.643</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>31785.47</v>
+        <v>37500.68</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>8976.172999999999</v>
+        <v>3260.963000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7797887342274206</v>
+        <v>0.9199992257426914</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>457.23</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>394.76</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -894,13 +894,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>108.29</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22360.4</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1014,13 +1014,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3037.16</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8236.48</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>507.91</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>270.66</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2697,10 +2697,10 @@
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1998.71</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>129.08</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="n">
         <v>0</v>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>1 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>3 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>3 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>3 de 38</t>
+          <t>0 de 38</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -2936,10 +2936,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2956,22 +2956,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2992,16 +2992,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>426.61</v>
+        <v>1166.13</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1166.13</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>457.23</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1166</v>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27</v>
+        <v>3777.36</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3777.36</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1846.26</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2500.23</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0</v>
+        <v>2898.21</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2898.21</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -3154,16 +3154,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>30185.39</v>
+        <v>1654.08</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1654.08</v>
+        <v>13787.67</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13787.67</v>
+        <v>22863.45</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>22863.45</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1654</v>
@@ -3208,16 +3208,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7650.16</v>
+        <v>7410.07</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7410.07</v>
+        <v>8184.38</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8184.38</v>
+        <v>11273.64</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>11273.64</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5390</v>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>1371.6</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6286.72</v>
+        <v>5754.13</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>5754.13</v>
+        <v>6712.94</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>6712.94</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>507.91</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8071.53</v>
+        <v>8681.9</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8681.9</v>
+        <v>5421.72</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5421.72</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>347.83</v>
+        <v>204.88</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>204.88</v>
+        <v>109.48</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>109.48</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0</v>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>7835.2</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7835.2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>2493.92</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2493.92</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>0</v>
@@ -3775,16 +3775,16 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>948.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0</v>
+        <v>1327.27</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1327.27</v>
+        <v>270.66</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>270.66</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0</v>
@@ -3916,10 +3916,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>2127.79</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>2127.79</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
@@ -3981,16 +3981,16 @@
     </row>
     <row r="39">
       <c r="C39" s="6" t="n">
-        <v>56444.04</v>
+        <v>37855.35</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>37855.35</v>
+        <v>40935.59</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>40935.59</v>
+        <v>39346.94</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>37500.68</v>
+        <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>13854</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1166</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>686</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8">
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1654</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="9">
@@ -3220,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5390</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11">
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13">
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1372</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="14">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="15">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="16">
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2420</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="22">
@@ -3571,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>131</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24">
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1035</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25">
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27">
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32">
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="34">
@@ -3922,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="37">
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>13854</v>
+        <v>39500</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3015,23 +3015,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANGAMARCA CURIPONA WILMA</t>
+          <t>ARIAS MEZA RONALD FABRICIO</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>3777.36</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1846.26</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4">
@@ -3042,23 +3042,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARIAS MEZA RONALD FABRICIO</t>
+          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3777.36</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1846.26</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3069,14 +3069,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARREAGA DELGADO ITALO TEOBALDO</t>
+          <t>BADILLO VERGARA MARIELA MARIA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>2898.21</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BADILLO VERGARA MARIELA MARIA</t>
+          <t>BARRETO CHAVARRIA RENZO DUVAL</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2898.21</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -3123,23 +3123,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BARRETO CHAVARRIA RENZO DUVAL</t>
+          <t>BORJA TORRES LETTY JANET</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0</v>
+        <v>1654.08</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>13787.67</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>22863.45</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="8">
@@ -3150,23 +3150,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BORJA TORRES LETTY JANET</t>
+          <t>BRIONES DIAZ HECTOR FERNANDO</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1654.08</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>13787.67</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22863.45</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3177,23 +3177,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRIONES DIAZ HECTOR FERNANDO</t>
+          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>7410.07</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>8184.38</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>11273.64</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="10">
@@ -3204,23 +3204,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BUENAÑO VITERI MARJORIE LETICIA</t>
+          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7410.07</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8184.38</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11273.64</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CALERO LOPEZ GISELLA JACKELINE</t>
+          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0</v>
+        <v>1371.6</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CARREÑO SANCHEZ ITALO VICENTE</t>
+          <t>CHASI PASTO ANGEL NOLBERTO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0</v>
+        <v>5754.13</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>6712.94</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="13">
@@ -3285,23 +3285,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CASA FERRETERIA FONG S.A. FERREFONG</t>
+          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1371.6</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>507.91</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -3312,14 +3312,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHASI PASTO ANGEL NOLBERTO</t>
+          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5754.13</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6712.94</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COMISARIATO DEL CONSTRUCTOR COMITRUCTOR S.A.</t>
+          <t>DEPODECON S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -3349,13 +3349,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>507.91</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CONTRATISTAS ACABADOS PARA LA CONTRUCCION JANDRI S.A.</t>
+          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEPODECON S.A.</t>
+          <t>ELECTROKOLER S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y SERVICIOS ELÉCTRICOS  ELEKTRICELL S.A.</t>
+          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ELECTROKOLER S.A.</t>
+          <t>FLORES PARRA CLEIVER YOEL</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>8681.9</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>5421.72</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="20">
@@ -3474,14 +3474,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FERRETERIA Y MADERAS S.A. MADEFER</t>
+          <t>GUILLEN PARRALES KATERINE MABEL</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>204.88</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>109.48</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21">
@@ -3501,14 +3501,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FLORES PARRA CLEIVER YOEL</t>
+          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8681.9</v>
+        <v>7835.2</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5421.72</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GRATEROL CASTILLO STEFFANY PAOLA ROSDALY</t>
+          <t>IMPORTELECTRIC S.A.S</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -3555,14 +3555,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GUILLEN PARRALES KATERINE MABEL</t>
+          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>204.88</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>109.48</v>
+        <v>2493.92</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24">
@@ -3582,11 +3582,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GUZMAN MAYORGA ROMINA SISNEY</t>
+          <t>INTROMEX S.A.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7835.2</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IMPORTELECTRIC S.A.S</t>
+          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INTERNEGOCIOS DE HIERRO S.A.</t>
+          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2493.92</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INTROMEX S.A.</t>
+          <t>LUI WONG ANGEL BOLIVAR</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3690,23 +3690,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ITURRALDE ROSALES FRANKLIN DAVID</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0</v>
+        <v>1327.27</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>270.66</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="29">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LINDAO MEJIA FERNANDO AGUILUCHO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LUI WONG ANGEL BOLIVAR</t>
+          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1327.27</v>
+        <v>0</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>270.66</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3808,191 +3808,29 @@
         <v>0</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0</v>
+        <v>2127.79</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>RODRIGUEZ PAILACHO VICENTE JONY</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>2127.79</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="6" t="n">
+      <c r="C33" s="6" t="n">
         <v>37855.35</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D33" s="6" t="n">
         <v>40935.59</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E33" s="6" t="n">
         <v>39346.94</v>
       </c>
-      <c r="F39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="6" t="n">
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
         <v>39500</v>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>-54.81</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -3136,7 +3136,7 @@
         <v>22863.45</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>-54.81</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8000</v>
@@ -3828,7 +3828,7 @@
         <v>39346.94</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0</v>
+        <v>-54.81</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>39500</v>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -3845,15 +3845,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3944,20 +3944,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREGADEROS DE COCINA</t>
+          <t>CERAMICA</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>199.5</v>
+        <v>3635</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>394.76</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-195.26</v>
+        <v>3635</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.97874686716792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GRIFERIAS</t>
+          <t>FREGADEROS DE COCINA</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>198.5</v>
+        <v>199.5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -3992,17 +3992,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAVABOS</t>
+          <t>GRIFERIAS</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>463</v>
+        <v>198.5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>463</v>
+        <v>198.5</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -4016,17 +4016,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NO RESURTIBLES</t>
+          <t>INODOROS</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>250</v>
+        <v>615</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>250</v>
+        <v>615</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -4040,17 +4040,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>LAVABOS</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -4064,20 +4064,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PANELES DECORATIVOS</t>
+          <t>NO RESURTIBLES</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>203.763</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3416.11</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-3212.347</v>
+        <v>250</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>16.76511437307068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -4112,20 +4112,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIEDRA SINTERIZADA</t>
+          <t>PANELES DECORATIVOS</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4600</v>
+        <v>203.763</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2963.85</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1636.15</v>
+        <v>203.763</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.6443152173913044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4136,20 +4136,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>31648</v>
+        <v>350</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>30725.96</v>
+        <v>0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>922.0400000000009</v>
+        <v>350</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.9708657735085945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4160,39 +4160,87 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>PIEDRA SINTERIZADA</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>35464</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-54.81</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>35518.81</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-0.001545510940672231</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>PUERTAS DE SEGURIDAD</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>1198.8</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="n">
+      <c r="D15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1198.8</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>40761.643</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>37500.68</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>3260.963000000001</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.9199992257426914</v>
+      <c r="C16" s="2" t="n">
+        <v>45197.643</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-54.81</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45252.453</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.001212673855581363</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MINUTOCORP S.A.</t>
+          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MUÑOZ FALCONES SERGIO BACILIO</t>
+          <t>PUCO TOAPANTA MARCO ANTONIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PUCO TOAPANTA MARCO ANTONIO</t>
+          <t>SANCHEZ BAJANA FRAK XAVIER</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SANCHEZ BAJANA FRAK XAVIER</t>
+          <t>SANCHEZ CORREA WILSON SERGIO</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SANCHEZ CORREA WILSON SERGIO</t>
+          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SOCIEDAD CIVIL Y COMERCIAL GRUPO MOLINA PROAÑO</t>
+          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SORIA AVELLAN RAFAEL HUMBERTO</t>
+          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2779,144 +2779,84 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LINDAO ZUÑIGA BRYAN JOSE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SOTOMAYOR ORTIZ LUIS JAVIER</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
-        </is>
-      </c>
-      <c r="R40" s="4" t="inlineStr">
-        <is>
-          <t>0 de 38</t>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>0 de 37</t>
         </is>
       </c>
     </row>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>1338.48</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="I36" s="2" t="n">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>479.69</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0</v>
+        <v>1344.33</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>0</v>
@@ -2806,32 +2806,32 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
+          <t>1 de 37</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
           <t>0 de 37</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>0 de 37</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>0 de 37</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>0 de 37</t>
-        </is>
-      </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>0 de 37</t>
+          <t>1 de 37</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>0 de 37</t>
+          <t>2 de 37</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>1338.48</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>2500</v>
@@ -3751,7 +3751,7 @@
         <v>2127.79</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
+        <v>2606.12</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>2000</v>
@@ -3768,7 +3768,7 @@
         <v>39346.94</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-54.81</v>
+        <v>3889.79</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>39500</v>
@@ -3793,7 +3793,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3963,13 +3963,13 @@
         <v>615</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>615</v>
+        <v>-167.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1.271707317073171</v>
       </c>
     </row>
     <row r="8">
@@ -4107,13 +4107,13 @@
         <v>970</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0</v>
+        <v>479.69</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>970</v>
+        <v>490.31</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.4945257731958763</v>
       </c>
     </row>
     <row r="14">
@@ -4131,13 +4131,13 @@
         <v>35464</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>-54.81</v>
+        <v>2628</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>35518.81</v>
+        <v>32836</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>-0.001545510940672231</v>
+        <v>0.07410331603879991</v>
       </c>
     </row>
     <row r="15">
@@ -4174,13 +4174,13 @@
         <v>45197.643</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>-54.81</v>
+        <v>3889.79</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45252.453</v>
+        <v>41307.853</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.001212673855581363</v>
+        <v>0.08606178866451066</v>
       </c>
     </row>
   </sheetData>

--- a/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
+++ b/data/LINDAO ZUÑIGA BRYAN JOSE.xlsx
@@ -455,7 +455,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0</v>
+        <v>37.08</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -2816,14 +2816,14 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
+          <t>1 de 37</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
           <t>0 de 37</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>0 de 37</t>
-        </is>
-      </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>1 de 37</t>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>2 de 37</t>
+          <t>3 de 37</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3076,7 +3076,7 @@
         <v>22863.45</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-54.81</v>
+        <v>49.75</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8000</v>
@@ -3768,7 +3768,7 @@
         <v>39346.94</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3889.79</v>
+        <v>3994.35</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>39500</v>
@@ -3791,7 +3791,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4035,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>104.56</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>-104.56</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -4131,13 +4131,13 @@
         <v>35464</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2628</v>
+        <v>2665.08</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32836</v>
+        <v>32798.92</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.07410331603879991</v>
+        <v>0.07514888337468982</v>
       </c>
     </row>
     <row r="15">
@@ -4174,13 +4174,13 @@
         <v>45197.643</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>3889.79</v>
+        <v>4031.43</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41307.853</v>
+        <v>41166.213</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.08606178866451066</v>
+        <v>0.08919558039785393</v>
       </c>
     </row>
   </sheetData>
